--- a/docs/downloads/York_Mills.xlsx
+++ b/docs/downloads/York_Mills.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D244"/>
+  <dimension ref="A1:D477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -545,17 +545,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pashka</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Paskulin</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pashka-paskulin@hotmail.com</t>
+          <t>yugogolf@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -567,17 +567,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Seyeon</t>
+          <t>krina</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Shah</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>banhee94@icloud.com</t>
+          <t>krina.shah1@gmail.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -589,17 +589,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Edun</t>
+          <t>Dorbyk</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Valdman</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>edunvaldman@yahoo.ca</t>
+          <t>alexdorbyk+@gmail.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -611,17 +611,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Pashka</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Golding</t>
+          <t>Paskulin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>michaelgolding77@hotmail.com</t>
+          <t>pashka-paskulin@hotmail.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -633,17 +633,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Seyeon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Waller</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>adam@pickleplexclub.ca</t>
+          <t>banhee94@icloud.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -655,17 +655,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nathalie</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Leduc</t>
+          <t>Motala</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nathalie@leduc.com</t>
+          <t>motalayusuf57@gmail.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -677,17 +677,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ah-chuen</t>
+          <t>Robertson</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kevin.ac.mu@gmail.com</t>
+          <t>stephanie.robertson@rogers.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -699,17 +699,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Louis</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kblackhole@yahoo.com</t>
+          <t>louis811023@gmail.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -721,17 +721,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Ilan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>O'brien</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mobrien@cclgroup.com</t>
+          <t>ilanbb9@gmail.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -743,17 +743,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Isay</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Khomyak</t>
+          <t>Golding</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>khomyakisay@gmail.com</t>
+          <t>michaelgolding77@hotmail.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -765,17 +765,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kretschmann</t>
+          <t>Waller</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>natekretschmann@gmail.com</t>
+          <t>adam@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -787,17 +787,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Jamie</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gilley</t>
+          <t>Robertson</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jason.gilley@uoit.net</t>
+          <t>jr900@protonmail.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -809,17 +809,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karin</t>
+          <t>Nathalie</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Damla</t>
+          <t>Leduc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>karin_damla@hotmail.com</t>
+          <t>nathalie@leduc.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -831,17 +831,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Yuridia</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Garcia</t>
+          <t>Ah-chuen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>yuyiisxd@gmail.com</t>
+          <t>kevin.ac.mu@gmail.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -853,17 +853,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bains</t>
+          <t>Shonfeld</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sarah.bains.13@gmail.com</t>
+          <t>lisashonfeld@gmail.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -875,17 +875,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cohen</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>aarongabrielcohen@gmail.com</t>
+          <t>kblackhole@yahoo.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -897,17 +897,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yiyi</t>
+          <t>Ada</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>852949906@qq.com</t>
+          <t>ma_ada@outlook.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -919,17 +919,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tillo</t>
+          <t>O'brien</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>coachjohn@pickleplexclub.ca</t>
+          <t>mobrien@cclgroup.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -941,17 +941,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Annie</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>alt.anemsgs@gmail.com</t>
+          <t>lauramoon.hm@gmail.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -963,17 +963,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mandar</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mandar1921@yahoo.co.in</t>
+          <t>e_g_benjamin@rogers.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -985,17 +985,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Isay</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bogert</t>
+          <t>Khomyak</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bogertja@gmail.com</t>
+          <t>khomyakisay@gmail.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1007,17 +1007,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>SEUNGYUB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Murphy</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jmurphy@ironbridgeequity.com</t>
+          <t>austin_power00@hotmail.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1029,17 +1029,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Paskulin</t>
+          <t>Kretschmann</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>exowill1@rogers.com</t>
+          <t>natekretschmann@gmail.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1051,17 +1051,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kleur</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Gilley</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>production@kleurvision.com</t>
+          <t>jason.gilley@uoit.net</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>Karin</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Yip</t>
+          <t>Damla</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>rebeccca.yip14@gmail.com</t>
+          <t>karin_damla@hotmail.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1095,17 +1095,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kawshik</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Basak</t>
+          <t>Drazilov</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>kawshik.basak96@gmail.com</t>
+          <t>rdrazilov@gmail.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1117,17 +1117,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Henrietta</t>
+          <t>Yuridia</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tsui</t>
+          <t>Garcia</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>henriettatsui@gmail.com</t>
+          <t>yuyiisxd@gmail.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1139,17 +1139,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tang</t>
+          <t>Bains</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>tangm614@gmail.com</t>
+          <t>sarah.bains.13@gmail.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1161,17 +1161,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Xiaohu</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Cohen</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>liuxiaohujacky@gmail.com</t>
+          <t>aarongabrielcohen@gmail.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Adel</t>
+          <t>Yiyi</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Stavitsky</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>adelstav@gmail.com</t>
+          <t>852949906@qq.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1205,17 +1205,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kitty</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Tillo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>kchan27@yahoo.com</t>
+          <t>coachjohn@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1227,17 +1227,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Leanne</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Lo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>leanne@pickleplexclub.ca</t>
+          <t>kevinjlo182@gmail.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1249,17 +1249,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Joel</t>
+          <t>Annie</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Douglas</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>joel.douglas123456789@gmail.com</t>
+          <t>alt.anemsgs@gmail.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1271,17 +1271,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Sally</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mills</t>
+          <t>Zhou</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>yorkmills@pickleplexclub.ca</t>
+          <t>sallyzhou999@gmail.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1293,17 +1293,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Naresh</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dale</t>
+          <t>Gopaul</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>matthew.dale@sympatico.ca</t>
+          <t>nareshgopaul@gmail.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1315,17 +1315,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Heesun</t>
+          <t>Elaine</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Choi</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>postaloutlet@hotmail.com</t>
+          <t>elaine.esther@gmail.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>david</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kremer</t>
+          <t>chong</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>rachel.kremer@outlook.com</t>
+          <t>davidbechong@gmail.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1359,17 +1359,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Mandar</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mignotte</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>acm.milan.m@gmail.com</t>
+          <t>mandar1921@yahoo.co.in</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1381,17 +1381,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Bogert</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>brianwlee17@gmail.com</t>
+          <t>bogertja@gmail.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1403,17 +1403,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ari</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Benlezrah</t>
+          <t>Scheer</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>lbenlezrah@rogers.com</t>
+          <t>nathanscheer2006@gmail.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1425,17 +1425,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Shaun</t>
+          <t>Yulika</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Linsao</t>
+          <t>Yoshida</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>shaun@pickleplexclub.ca</t>
+          <t>yulikayoshida@gmail.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1447,15 +1447,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Shirley</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lee</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>Lasola</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mayalasola@gmail.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1465,15 +1469,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Congcong</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>Aue</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>aaue597@gmail.com</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1483,15 +1491,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Navneet</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bal</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>Murphy</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>jmurphy@ironbridgeequity.com</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1501,15 +1513,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Scott</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>Paskulin</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>exowill1@rogers.com</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1519,15 +1535,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>YOONHWA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>LEE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>lee.yoonhwa@gmail.com</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1537,15 +1557,19 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Shilpa</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pal</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>Eberlin</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>warren.eberlin@icloud.com</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1555,15 +1579,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Jongmun</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Woo</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>calcaneous@gmail.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1573,15 +1601,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Kleur</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>production@kleurvision.com</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1591,15 +1623,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Allyano</t>
+          <t>Maxmillian</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Badrie-Deen</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>Moon</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>maxmillianmoon@gmail.com</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1609,15 +1645,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Rebecca</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>Yip</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>rebeccca.yip14@gmail.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1627,15 +1667,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Royce</t>
+          <t>Kawshik</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>Basak</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>kawshik.basak96@gmail.com</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1645,15 +1689,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jiyaan</t>
+          <t>Henrietta</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Shukla</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>Tsui</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>henriettatsui@gmail.com</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1663,15 +1711,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Lai Ming</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kwan</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>Park</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>qkrektmf913@hotmail.com</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1681,15 +1733,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Chapman</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ma</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>Tang</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>tangm614@gmail.com</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1699,15 +1755,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dezhong</t>
+          <t>Xiaohu</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Chen</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>liuxiaohujacky@gmail.com</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1717,15 +1777,19 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Myles</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Romero</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>Chan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>pensive-dime-0u@icloud.com</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1735,15 +1799,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Bernard</t>
+          <t>Adel</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chan</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>Stavitsky</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>adelstav@gmail.com</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1753,15 +1821,19 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ching</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>Aquino</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>mickay0928@gmail.com</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1771,15 +1843,19 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Kitty</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Popik</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>kchan27@yahoo.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1789,15 +1865,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Stella</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cohen</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>Jeon</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ppll3825@gmail.com</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1807,15 +1887,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Leanne</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jivov</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>leanne@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1825,15 +1909,19 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Dyllan</t>
+          <t>Nadya</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Opinaldo</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>Iswari</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>nadya.iswari@gmail.com</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1843,15 +1931,19 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Malcolm</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Beach</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>Douglas</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>joel.douglas123456789@gmail.com</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1861,15 +1953,19 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Noime</t>
+          <t>York</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Manalo</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>Mills</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1879,15 +1975,19 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nixon</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>Dale</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>matthew.dale@sympatico.ca</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1897,15 +1997,19 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jayden</t>
+          <t>Heesun</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Woo</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>Choi</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>postaloutlet@hotmail.com</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1915,15 +2019,19 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ellen</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kurtz-Cohen</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>Kremer</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>rachel.kremer@outlook.com</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1933,15 +2041,19 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ridley</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tsui</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>Mignotte</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>acm.milan.m@gmail.com</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1951,15 +2063,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Yang</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>brianwlee17@gmail.com</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1969,15 +2085,19 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Johnnie</t>
+          <t>Herman</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ma</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>Szeto</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>hpszeto@rogers.com</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1987,15 +2107,19 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Leveson</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>Mackay</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>kcmackay742@gmail.com</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -2005,15 +2129,19 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Abigail</t>
+          <t>Dilesh</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>Bhullar</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>bhullardilesh@gmail.com</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -2023,15 +2151,19 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sidney</t>
+          <t>Shaun</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Scott</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>Linsao</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>shaun@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -2041,15 +2173,19 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Wojtek</t>
+          <t>Ronny</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>Kofman</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ronnykofman@gmail.com</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -2059,12 +2195,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Geoff</t>
+          <t>Shirley</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Anderton</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -2077,12 +2213,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Addy</t>
+          <t>Congcong</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Zhang</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2095,12 +2231,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Maxwell</t>
+          <t>Navneet</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Leveson</t>
+          <t>Bal</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -2113,12 +2249,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Du</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2131,12 +2267,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2149,12 +2285,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Shilpa</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Beach</t>
+          <t>Pal</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -2167,12 +2303,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Reid</t>
+          <t>Woo</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2185,12 +2321,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Maya</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -2203,12 +2339,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Mathis</t>
+          <t>Allyano</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Leveson</t>
+          <t>Badrie-Deen</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2221,12 +2357,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -2239,12 +2375,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Gavin</t>
+          <t>Royce</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tsui</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -2257,12 +2393,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Jiyaan</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Goertz</t>
+          <t>Shukla</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2275,12 +2411,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ryab</t>
+          <t>Lai Ming</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bolger</t>
+          <t>Kwan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2293,12 +2429,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Lainey</t>
+          <t>Chapman</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2311,12 +2447,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Dezhong</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bolger</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2329,12 +2465,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Myles</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Aceto</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2347,12 +2483,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Bernard</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Yin</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -2365,12 +2501,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Ching</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -2383,12 +2519,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Agnes</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tong</t>
+          <t>Popik</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2401,12 +2537,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Michael A</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Popik</t>
+          <t>Cohen</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -2419,12 +2555,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Matteo</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Zilli</t>
+          <t>Jivov</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -2437,12 +2573,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Gwen</t>
+          <t>Dyllan</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Chasson</t>
+          <t>Opinaldo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -2455,12 +2591,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ankur</t>
+          <t>Malcolm</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kulshrestha</t>
+          <t>Beach</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -2473,12 +2609,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>Noime</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Jivov</t>
+          <t>Manalo</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2491,12 +2627,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Nixon</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2509,12 +2645,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Jayden</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Chasson</t>
+          <t>Woo</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2527,12 +2663,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ruchira</t>
+          <t>Ellen</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Roy</t>
+          <t>Kurtz-Cohen</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2545,12 +2681,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Ridley</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sulkowski</t>
+          <t>Tsui</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2563,12 +2699,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Brent</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Yang</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2581,12 +2717,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Johnnie</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Aceto</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2599,12 +2735,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Ray</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cao</t>
+          <t>Leveson</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2617,12 +2753,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Abigail</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Sulkowski</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2635,12 +2771,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>hunter</t>
+          <t>Sidney</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>julien-dolphin</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2653,12 +2789,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Wojtek</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2671,12 +2807,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Milad</t>
+          <t>Geoff</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Modir</t>
+          <t>Anderton</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2689,12 +2825,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Brandon Scott</t>
+          <t>Addy</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2707,12 +2843,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Maxwell</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Aceto</t>
+          <t>Leveson</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2725,12 +2861,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Du</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2743,12 +2879,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2761,12 +2897,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kung</t>
+          <t>Beach</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2779,12 +2915,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Lalique K Y</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Reid</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2797,12 +2933,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Jimmy</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Yu</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2815,12 +2951,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Lathan</t>
+          <t>Mathis</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Solis</t>
+          <t>Leveson</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2833,12 +2969,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Beach</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2851,12 +2987,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Jivov</t>
+          <t>Tsui</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -2869,12 +3005,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Zou</t>
+          <t>Goertz</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -2887,12 +3023,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Arlene</t>
+          <t>Ryab</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FitzGerald</t>
+          <t>Bolger</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -2905,12 +3041,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sakura</t>
+          <t>Lainey</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Shimada</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -2923,12 +3059,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Cedric</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Chasson</t>
+          <t>Bolger</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -2941,12 +3077,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Popik</t>
+          <t>Aceto</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -2959,12 +3095,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Adrian</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Yin</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -2977,12 +3113,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Axel</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -2995,12 +3131,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Agnes</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Joo</t>
+          <t>Tong</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -3013,19 +3149,15 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Bryle</t>
+          <t>Michael A</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Flores</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>brylefanshawe@gmail.com</t>
-        </is>
-      </c>
+          <t>Popik</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3035,12 +3167,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Mika</t>
+          <t>Matteo</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Zilli</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -3053,19 +3185,15 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Amir</t>
+          <t>Gwen</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Haniff</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>amirhaniff@hotmail.com</t>
-        </is>
-      </c>
+          <t>Chasson</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3075,12 +3203,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Ankur</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ho</t>
+          <t>Kulshrestha</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -3093,12 +3221,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Abuan</t>
+          <t>Jivov</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -3111,12 +3239,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>O'Connor</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -3129,12 +3257,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Sevier</t>
+          <t>Chasson</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -3147,12 +3275,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Celica</t>
+          <t>Ruchira</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Roy</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -3165,19 +3293,15 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Eluxni</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Kanesathas</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>eluxthas@icloud.com</t>
-        </is>
-      </c>
+          <t>Sulkowski</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3187,12 +3311,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Ronan</t>
+          <t>Brent</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -3205,12 +3329,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Dakota</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Fernandes</t>
+          <t>Aceto</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -3223,12 +3347,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Ray</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Zabaneh</t>
+          <t>Cao</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -3241,12 +3365,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Celine</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Zabaneh</t>
+          <t>Sulkowski</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -3259,12 +3383,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Chanie</t>
+          <t>hunter</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Yucor</t>
+          <t>julien-dolphin</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -3277,12 +3401,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Raphael</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Del Rosario</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -3295,12 +3419,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Dario</t>
+          <t>Milad</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Jamalzadeh</t>
+          <t>Modir</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -3313,12 +3437,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Brandon Scott</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -3331,19 +3455,15 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ali</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>karimi</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>alikarimi1313@hotmail.com</t>
-        </is>
-      </c>
+          <t>Aceto</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3353,19 +3473,15 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Lane</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ritcey</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>sueritcey@gmail.com</t>
-        </is>
-      </c>
+          <t>Scott</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3375,12 +3491,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Zaina</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Zabaneh</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -3393,12 +3509,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Aria</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Fernandes</t>
+          <t>Kung</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -3411,12 +3527,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Maggie</t>
+          <t>Lalique K Y</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Chiu</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -3429,12 +3545,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Nirmaljeet</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -3447,19 +3563,15 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Brian J</t>
+          <t>Lathan</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Quinlan</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>brianquinlan@sympatico.ca</t>
-        </is>
-      </c>
+          <t>Solis</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3469,12 +3581,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>diana</t>
+          <t>Cadence</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dodd</t>
+          <t>Beach</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -3487,12 +3599,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Jivov</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -3505,19 +3617,15 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TASLIM</t>
+          <t>Lu</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SOMANI</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>taslimsomani@gmail.com</t>
-        </is>
-      </c>
+          <t>Zou</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3527,12 +3635,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Emmanuel</t>
+          <t>Arlene</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>FitzGerald</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -3545,12 +3653,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Ashley</t>
+          <t>Sakura</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Shimada</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -3563,12 +3671,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Jasmine</t>
+          <t>Cedric</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Xiao</t>
+          <t>Chasson</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -3581,12 +3689,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Bruce</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Popik</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -3599,15 +3707,19 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STEVEN</t>
+          <t>Jemuel</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Li</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr"/>
+          <t>Bonaobra</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>jemboy177@hotmail.com</t>
+        </is>
+      </c>
       <c r="D165" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3617,15 +3729,19 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>Debbie</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Yang</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr"/>
+          <t>Panait</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>debbiepanait@hotmail.com</t>
+        </is>
+      </c>
       <c r="D166" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3635,12 +3751,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Janina</t>
+          <t>Adrian</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>KLOPSCH</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -3653,19 +3769,15 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Axel</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Easey</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>jenroberts6@gmail.com</t>
-        </is>
-      </c>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3675,12 +3787,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Joo</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -3693,15 +3805,19 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Hendrik</t>
+          <t>Bryle</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>VanderMeulen</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
+          <t>Flores</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>brylefanshawe@gmail.com</t>
+        </is>
+      </c>
       <c r="D170" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3711,12 +3827,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Justus</t>
+          <t>Mika</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -3729,15 +3845,19 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Amir</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
+          <t>Haniff</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>amirhaniff@hotmail.com</t>
+        </is>
+      </c>
       <c r="D172" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3747,15 +3867,19 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Esther</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Li</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr"/>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>caroline826yang@hotmail.com</t>
+        </is>
+      </c>
       <c r="D173" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3765,12 +3889,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Tammie</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Fong</t>
+          <t>Ho</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -3783,12 +3907,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Yin</t>
+          <t>Abuan</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -3801,12 +3925,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Bennett</t>
+          <t>O'Connor</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -3819,12 +3943,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Macdonald</t>
+          <t>Sevier</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -3837,12 +3961,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Suhanee</t>
+          <t>Celica</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Sood</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -3855,15 +3979,19 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Mylo</t>
+          <t>Eluxni</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Cotton</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr"/>
+          <t>Kanesathas</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>eluxthas@icloud.com</t>
+        </is>
+      </c>
       <c r="D179" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3873,17 +4001,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Rohit</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Couse</t>
+          <t>Mehra</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>jcouse@segalgcse.com</t>
+          <t>r-smehra@rogers.com</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -3895,15 +4023,19 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Josiah</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Lam</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr"/>
+          <t>Phung</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>benjaminkwongmanphung@gmail.com</t>
+        </is>
+      </c>
       <c r="D181" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3913,15 +4045,19 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Aceto</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr"/>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>christine.nguyen15@gmail.com</t>
+        </is>
+      </c>
       <c r="D182" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3931,15 +4067,19 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Brad</t>
+          <t>Anatoli</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Cotton</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
+          <t>Naoumov</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>anaoumov@gmail.com</t>
+        </is>
+      </c>
       <c r="D183" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3949,15 +4089,19 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Cotton</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr"/>
+          <t>Palalon</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>honeypalalon@gmail.com</t>
+        </is>
+      </c>
       <c r="D184" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3967,12 +4111,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Vic</t>
+          <t>Ronan</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Suan</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -3985,19 +4129,15 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Dakota</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Cummings</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>mwcummings@hotmail.ca</t>
-        </is>
-      </c>
+          <t>Fernandes</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4007,12 +4147,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Hua</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Shi</t>
+          <t>Zabaneh</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -4025,12 +4165,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Gila</t>
+          <t>Celine</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Kohen Rydlewicz</t>
+          <t>Zabaneh</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4043,12 +4183,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Chanie</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Aceto</t>
+          <t>Yucor</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -4061,12 +4201,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Care</t>
+          <t>Raphael</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Dodd</t>
+          <t>Del Rosario</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -4079,12 +4219,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Godfrey</t>
+          <t>Dario</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Yeung</t>
+          <t>Jamalzadeh</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -4097,19 +4237,15 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>claudine</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Lukawesky</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>davidclaudie@sympatico.ca</t>
-        </is>
-      </c>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4119,15 +4255,19 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>ali</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Suan</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr"/>
+          <t>karimi</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>alikarimi1313@hotmail.com</t>
+        </is>
+      </c>
       <c r="D193" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4137,15 +4277,19 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr"/>
+          <t>Ritcey</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>sueritcey@gmail.com</t>
+        </is>
+      </c>
       <c r="D194" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4155,12 +4299,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Kieran</t>
+          <t>Zaina</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Lai</t>
+          <t>Zabaneh</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -4173,19 +4317,15 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Hafsa</t>
+          <t>Aria</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Esmail</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>admin@powerofwordsacademy.ca</t>
-        </is>
-      </c>
+          <t>Fernandes</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4195,15 +4335,19 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Darryl</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Fortes</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr"/>
+          <t>Bui</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>thangbuidayielts@gmail.com</t>
+        </is>
+      </c>
       <c r="D197" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4213,12 +4357,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Henrietta</t>
+          <t>Maggie</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Tsui</t>
+          <t>Chiu</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -4231,12 +4375,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Nirmaljeet</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Simunovic</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -4249,15 +4393,19 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Cole</t>
+          <t>Brian J</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Billinkoff</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr"/>
+          <t>Quinlan</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>brianquinlan@sympatico.ca</t>
+        </is>
+      </c>
       <c r="D200" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4267,12 +4415,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Bobby</t>
+          <t>diana</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Cancelli</t>
+          <t>Dodd</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -4285,12 +4433,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Jake</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Billinkoff</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -4303,15 +4451,19 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Jennie</t>
+          <t>TASLIM</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Mohabir</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr"/>
+          <t>SOMANI</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>taslimsomani@gmail.com</t>
+        </is>
+      </c>
       <c r="D203" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4321,12 +4473,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Rachelle</t>
+          <t>Emmanuel</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -4339,12 +4491,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Ashley</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Girard</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -4357,12 +4509,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Kathleen</t>
+          <t>Jasmine</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Nadon</t>
+          <t>Xiao</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -4375,12 +4527,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Bruce</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Nadon</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -4393,12 +4545,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Teos</t>
+          <t>STEVEN</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Vaccaro</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -4411,12 +4563,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Jackie</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Yang</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -4429,12 +4581,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Jisoo</t>
+          <t>Janina</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Maynard</t>
+          <t>KLOPSCH</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -4447,15 +4599,19 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Karam</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr"/>
+          <t>Easey</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>jenroberts6@gmail.com</t>
+        </is>
+      </c>
       <c r="D211" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4465,12 +4621,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Almaria</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -4483,12 +4639,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Sisily</t>
+          <t>Hendrik</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Solis</t>
+          <t>VanderMeulen</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -4501,12 +4657,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Lilybeth</t>
+          <t>Justus</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Solis</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -4519,12 +4675,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Teos</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Vaccaro</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -4537,12 +4693,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Ksenia</t>
+          <t>Esther</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Vaccaro</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -4555,12 +4711,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Tammie</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Nicholl</t>
+          <t>Fong</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -4573,12 +4729,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Nicholl</t>
+          <t>Yin</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -4591,12 +4747,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Tay</t>
+          <t>Bennett</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -4609,12 +4765,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Asllan</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Macdonald</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -4627,12 +4783,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Giselle</t>
+          <t>Suhanee</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Del Rosario</t>
+          <t>Sood</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -4645,12 +4801,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Mylo</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Jenkins</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -4663,15 +4819,19 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Chin</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr"/>
+          <t>Couse</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>jcouse@segalgcse.com</t>
+        </is>
+      </c>
       <c r="D223" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4681,12 +4841,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Josiah</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Cheung</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -4699,12 +4859,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Kiara</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Bici</t>
+          <t>Aceto</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -4717,12 +4877,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Brad</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jin</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -4735,12 +4895,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Vicky</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Su</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -4753,12 +4913,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Vic</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Pileggi</t>
+          <t>Suan</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -4771,15 +4931,19 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Fiona</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Wang</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr"/>
+          <t>Cummings</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>mwcummings@hotmail.ca</t>
+        </is>
+      </c>
       <c r="D229" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4789,12 +4953,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Brittany</t>
+          <t>Hua</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Horan</t>
+          <t>Shi</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -4807,12 +4971,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Gila</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Folletet</t>
+          <t>Kohen Rydlewicz</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -4825,12 +4989,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Ruchira</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Kulkarni</t>
+          <t>Aceto</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -4843,12 +5007,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Annie</t>
+          <t>Care</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Tran</t>
+          <t>Dodd</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -4861,12 +5025,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Lilian</t>
+          <t>Godfrey</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Jiang</t>
+          <t>Yeung</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -4879,15 +5043,19 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>claudine</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Lam</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr"/>
+          <t>Lukawesky</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>davidclaudie@sympatico.ca</t>
+        </is>
+      </c>
       <c r="D235" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4897,12 +5065,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Pamela</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Ip</t>
+          <t>Suan</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -4915,12 +5083,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Dana</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -4933,12 +5101,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Kieran</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Kitt</t>
+          <t>Lai</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -4951,15 +5119,19 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Mack</t>
+          <t>Hafsa</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Lapointe</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr"/>
+          <t>Esmail</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>admin@powerofwordsacademy.ca</t>
+        </is>
+      </c>
       <c r="D239" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4969,19 +5141,15 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Jay</t>
+          <t>Darryl</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Latiff</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>jaythefungi@proton.me</t>
-        </is>
-      </c>
+          <t>Fortes</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4991,12 +5159,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Lin</t>
+          <t>Henrietta</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>Tsui</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -5009,12 +5177,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Mikhael</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>Simunovic</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -5027,12 +5195,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Anh</t>
+          <t>Cole</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Billinkoff</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -5045,16 +5213,4898 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Bobby</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Cheung</t>
+          <t>Cancelli</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Jake</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Billinkoff</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Jennie</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Mohabir</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Rachelle</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Patrick</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Mateo</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Girard</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Schiessl</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>maikonsch@gmail.com</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Brandon</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Gross</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>gross.brandon29@gmail.com</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Kathleen</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Nadon</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Nadon</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Bretilu</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>mebretilu.merb@gmail.com</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Leung</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>lilyleung0519@gmail.com</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Teos</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Vaccaro</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Carla</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>carlajoyce@rogers.com</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Jackie</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Chan</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Jisoo</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Maynard</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Dhiren</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Jain</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>dhiren.d.jain@gmail.com</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Karam</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Almaria</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Sisily</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Solis</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Lilybeth</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Solis</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Teos</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Vaccaro</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Ksenia</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Vaccaro</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Logan</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Nicholl</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Brooke</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Nicholl</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Divya J</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Sharma</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>divya.djs@outlook.com</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Nathan</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Tay</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Asllan</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Giselle</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Del Rosario</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Jenkins</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Brandon</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Chin</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>wlee75@gmail.com</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Cheung</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Kiara</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Bici</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Kathy</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Jin</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Vicky</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Su</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Amanda</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Pileggi</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Fiona</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Brittany</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Horan</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Folletet</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Ruchira</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Kulkarni</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Annie</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Tran</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Lilian</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Jiang</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Lam</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Pamela</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Ip</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Arlie</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Cuaresma</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>arlieangela@gmail.com</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Ehsan</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Parsi</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>ehsanparssiii@gmail.com</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Erika</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Lagunzad</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>erikalagunzad@gmail.com</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Dana</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Ma</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Kitt</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Bumkun</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>qjarmsl94@gmail.com</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Mack</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Lapointe</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Edward</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Greenspon</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>egreenspon@gmail.com</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Latiff</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>jaythefungi@proton.me</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Lin</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Lu</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Mikhael</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Anh</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Ysabelle</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Aguilera</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>ysabelle@live.com</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Einer John</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Cupino</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>einer.cupino@gmail.com</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Patrick</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Cheung</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>McCharles</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>jan.mccharles@gmail.com</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Toby</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Goldberg</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>tirtzag52@gmail.com</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Liza</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Benkovitch</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>liza@d8teclub.com</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Dávalos ucha</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Reena</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Fernandez</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>reenaf879@gmail.com</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Dana</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>danatanuecoz21@gmail.com</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Xuhong</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>lucyl777888@gmail.com</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Rodrigues</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>nrodrigues@cihi.ca</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Duy</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Ho</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Nasim</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Hashemi</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Moy</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>jordanmoy94@gmail.com</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Ashley</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Vu</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Dong</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Daisy</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Xu</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Kat</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Bhamra</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>simranb1395@gmail.com</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Sophia</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Geronimo</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>aihpysabelle@gmail.com</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Pinthong</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>sita_beau@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Ferreira</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>getaclue1962@gmail.com</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Naznin</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Kamani</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>naznin.kamani@gmail.com</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Shikha</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Kothari</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Ernest</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Cueva</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>ernestcesar.cueva@gmail.com</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Carmen</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Leung</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>zoee121@gmail.com</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Tracy</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Timosa</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Mary</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Rabino</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>maryaizarabino@gmail.com</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Marie Tracy</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Timosa</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>tracytimosa90@outlook.com</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Kurt</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Davis</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>kurtodavis@gmail.com</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Corinne</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Moehring</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>cori182@gmail.com</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Dhruvi</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Modi</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>dhruvi.modi1112@gmail.com</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Zabaleta</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>zabaletacopa@outlook.com</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Davis</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Suzanne</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Robinson Davis</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>suzie1rob@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Robert</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>robert.wang@gmail.com</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Sean</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>fg008kimo@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Alexandra</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Galon</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>alexandragalon21@gmail.com</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Hsieh</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Maggie</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>maggie.v.lee510@gmail.com</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>mattdw25@gmail.com</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Xiao</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>ljxrachel420@gmail.com</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>jennifer.chen@live.ca</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Leslie</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Yang</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>alex2023yang@gmail.com</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Philip</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Chan</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>philipchan92@gmail.com</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Leung</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>paul.cfleung@gmail.com</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Royce</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>McCutcheon</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>mr.mathew.thomas@gmail.com</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>George</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Leong</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>george_leong@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Shibin</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>shibinsmail@gmail.com</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Aristo</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>officialaristok@gmail.com</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Alissa</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Sherman</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>shermanator@rogers.com</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Mehlu</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>rachelolxx@gmail.com</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Nevyn</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Pillai</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>nevynpillai@aol.com</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Joanna</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>joannawang0516@gmail.com</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Tommy</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Lam</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>lamtommybusiness@gmail.com</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Everly</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>mycket0070@gmail.com</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Catherine</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>ckwlai@gmail.com</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Zahid</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>zahid.kachwala@gmail.com</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Shuli</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Rotenberg</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>shulislp@gmail.com</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Rebecca</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Ko</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>rebecca.ko@jig.to</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Cho</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>kevincho3815@gmail.com</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Urvashi</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Chauhan</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>urvashi.chauhan@clearscore.com</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Ria</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Tio</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>yamaetio@gmail.com</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Cheng</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>rwcheng@umich.edu</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Jacqueline</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Tse</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>jackietse@gmail.com</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Lulu</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Cusimano</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>loucusi8@gmail.com</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>ALIREZA</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>ATAEIPOUR</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>alireza.ataeipour@gmail.com</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Gazi Mahmudul</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Hasan</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>gmh.mahin@gmail.com</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Sheu</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>laurasheu@gmail.com</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>chasemendoza@icloud.com</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Epstein</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>iepstein2018@gmail.com</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Mallory</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Fung</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>fungmallory@gmail.com</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Roselle</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Mendez</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>rosellemendez1981@gmail.com</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Vita</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Kwan</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>vitakwanwt@gmail.com</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Dharsha</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Sundarampillai</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>dharsha.sundar@gmail.com</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Veronica</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Chan</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>lettervtoc@gmail.com</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Ku</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>danielku20@gmail.com</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Louis</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Zhao</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>louiszhao02@gmail.com</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Carstin</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Hao</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>carstin.hao@gmail.com</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Ayokunle</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Bamisile-Aje</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>admit_kunle@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Sreejayan</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Rama Syam</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>sreejayan.rs@outlook.com</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Dahlia</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Lesh</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>d.lesh@rogers.com</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Marlon</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Canales</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>marlon.canales22@gmail.com</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Jayden</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Vuong</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>jay_lv151@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Ellen</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Auster</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>e.r.auster@gmail.com</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Bhavish</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Verma</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>bhav7@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Athavan</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Karunakaran</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>athavan.karunakaran@gmail.com</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Marcie</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Somers</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>m_somers@rogers.com</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Zhuang</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>yiwei95@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Yu</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>jonathanyu91@icloud.com</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Sypher</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>davsyp@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Ploy</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Jamroonjamroenpit</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>pjamroon@gmail.com</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Natan</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>itsleo797@gmail.com</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Xi</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Mei</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>xm518@nyu.edu</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Joe</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Banerjee</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>nilabjo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Bhanu</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Mehta</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>bhanu.mehta@empire.ca</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Jessy</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>jessyjieli@gmail.com</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Dora</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Qian</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>kumakoq@gmail.com</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>zzt0416@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Ortega</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>ellieoh21@gmail.com</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Jovan</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Bursac</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>bursj447@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Jeffrey</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Cukier</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>jcukier99@gmail.com</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Alvarez</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>juanalpi96@gmail.com</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Solita</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Hernandez</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>solita.takacs@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Chi</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Quach</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>mesamune@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Ravi</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>ravisingh2491@gmail.com</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Krystal</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>krystalzhang020503@gmail.com</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Del rosario</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Sheena Joy</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Del Rosario</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>sheena.dlrsrio@gmail.com</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Del Rosario</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>camillejoydelrosario@gmail.com</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Patrick</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Laurinaria</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>fitzpartich@gmail.com</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Sunder</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Sauri</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>sundersauri@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Winson</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Guo</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>winsonguocc@gmail.com</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Pui</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>sammypui2@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>jennylib2@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Pink</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>laurapink@rogers.com</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Astrid</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Prado</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>pradoastrid@rocketmail.com</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Kan</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Ma</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>heung.ma@medportal.ca</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Shane</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Sucaldito</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>shanesucaldito@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>AJ</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Hum</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>humamanda@gmail.com</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Liang</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>awsliang@gmail.com</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Lis</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>ana.lis1224@outlook.com</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Suzie</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>suzanneskim94@gmail.com</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Fung</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>weeliyum.f@gmail.com</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Gordon</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>kyle_gordon_19@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Marc</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Ah chin kow</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>marcack14@gmail.com</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Pena</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>alejandroleal3c@gmail.com</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Aakash</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Logavi</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>aakashlogavi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Sami</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Yakan</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>pizzaturle@gmail.com</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>jatin</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>maru</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>ja3maru@gmail.com</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Ciara</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Sison</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>ciara.sison@gmail.com</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Soong</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>kkysoong@gmail.com</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Umali</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>mumali90@gmail.com</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Moy</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>patricia.moy_rnc@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Hittner</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>jenniferhittner@gmail.com</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Paulette</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Gill-Morton</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>paulettegillmorton@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Evelyn</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Baek</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>evelynbaek9843@gmail.com</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Sison</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>nancy.moy@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Jaclyn</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Arts</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>jaclyn_arts@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Joel</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>phone.jkxa@gmail.com</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Cooney</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Galina</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Lad</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Parham</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Kazemi</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>parhamkazemi50@gmail.com</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Cooney</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Volodimir</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Bondarenko</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>vobond@gmail.com</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Sung</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>wwlsung@gmail.com</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Sahar</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Winnie</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Szeto</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>winnietheszeto@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Talia</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Goldberg</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>tgoldberg92@gmail.com</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Srujal</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>srujalpatel22@gmail.com</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Darius</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Juarez</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>dariusjuarez24@gmail.com</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Arav</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Surati</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>surtidev7@gmail.com</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Samantha</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Levin</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>samanthasarahlevin@gmail.com</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Mahdiyar</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Alavi</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>mahdiyar.edu@gmail.com</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Owen Jacob</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Go</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>owen.go2021@gmail.com</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Meenakshi</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>minaxi.arya@gmail.com</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Greenspan</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>jaimegreenspan@gmail.com</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Shubh</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Ramchandani</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>shxbh007@gmail.com</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Rose Marie</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Sumobay</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>rm661917@gmail.com</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Robyn</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Steidman</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>rsteidman@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Sebastien</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Bonami</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>sebastien.bonami@gmail.com</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Niloufar</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Habashizadeh</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>niloofar.hz@icloud.com</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>superdupr@gmail.com</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Pouya</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Senemari</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>pouya.senemari@gmail.com</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>J Rome</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Yu</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>yu_jrome@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Edmund</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Siu</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>edmundsiu33@gmail.com</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Chase</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Clifton</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>chasewc@gmail.com</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Samaneh</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Yazdanipour</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>yazdanipur.sm@gmail.com</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Mahir</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Quddus</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>dhrubomahirul@gmail.com</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Alireza</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Nourany</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>alireza.nourany@gmail.com</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Azeem</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Hussain</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>hussain.azeem@gmail.com</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Salama</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Karim</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Lam</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>alexlam1994@gmail.com</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Lau</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>justin.hk.lau@outlook.com</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Ong</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>ongkpl@gmail.com</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Yoomi</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Oh</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>raccoontale1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
         </is>

--- a/docs/downloads/York_Mills.xlsx
+++ b/docs/downloads/York_Mills.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D279"/>
+  <dimension ref="A1:D371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -501,17 +501,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mairéad</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mairead.ryan@gmail.com</t>
+          <t>michaelwwang@yahoo.ca</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -523,17 +523,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shirley</t>
+          <t>Mairéad</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fong</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>shirleefong@gmail.com</t>
+          <t>mairead.ryan@gmail.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -545,17 +545,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Shirley</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tibayan</t>
+          <t>Fong</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>itibayan@hotmail.com</t>
+          <t>shirleefong@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -567,17 +567,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pui</t>
+          <t>Tibayan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>spui@joola.ca</t>
+          <t>itibayan@hotmail.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -589,17 +589,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pashka</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Paskulin</t>
+          <t>Pui</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pashka-paskulin@hotmail.com</t>
+          <t>spui@joola.ca</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -611,17 +611,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Seyeon</t>
+          <t>Pashka</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Paskulin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>banhee94@icloud.com</t>
+          <t>pashka-paskulin@hotmail.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -633,17 +633,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Seyeon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Golding</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>michaelgolding77@hotmail.com</t>
+          <t>banhee94@icloud.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -655,17 +655,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Jeffrey</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Waller</t>
+          <t>Chang</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>adam@pickleplexclub.ca</t>
+          <t>asianhockeychampionship@gmail.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -677,17 +677,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nathalie</t>
+          <t>roger</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Leduc</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nathalie@leduc.com</t>
+          <t>yang2650876835@gmail.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -699,17 +699,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ah-chuen</t>
+          <t>Golding</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kevin.ac.mu@gmail.com</t>
+          <t>michaelgolding77@hotmail.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -721,17 +721,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Waller</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kblackhole@yahoo.com</t>
+          <t>adam@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -743,17 +743,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Lucy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>O'brien</t>
+          <t>Wu</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mobrien@cclgroup.com</t>
+          <t>lucywu2014@gmail.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -765,17 +765,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Isay</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Khomyak</t>
+          <t>Woo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>khomyakisay@gmail.com</t>
+          <t>bubulime@gmail.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -787,17 +787,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Sheena</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kretschmann</t>
+          <t>Yang</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>natekretschmann@gmail.com</t>
+          <t>yipsheena@gmail.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -809,17 +809,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gilley</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jason.gilley@uoit.net</t>
+          <t>julia.ann.nurse@gmail.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -831,17 +831,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Karin</t>
+          <t>Nathalie</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Damla</t>
+          <t>Leduc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>karin_damla@hotmail.com</t>
+          <t>nathalie@leduc.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -853,17 +853,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Yuridia</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Garcia</t>
+          <t>Ah-chuen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>yuyiisxd@gmail.com</t>
+          <t>kevin.ac.mu@gmail.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -875,17 +875,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Alan K</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bains</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sarah.bains.13@gmail.com</t>
+          <t>bulubaba2021@gmail.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -897,17 +897,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cohen</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>aarongabrielcohen@gmail.com</t>
+          <t>kblackhole@yahoo.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -919,17 +919,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Yiyi</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>O'brien</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>852949906@qq.com</t>
+          <t>mobrien@cclgroup.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -941,17 +941,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tillo</t>
+          <t>Chui</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>coachjohn@pickleplexclub.ca</t>
+          <t>chuiaurora@hotmail.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -963,17 +963,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Annie</t>
+          <t>Isay</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Khomyak</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>alt.anemsgs@gmail.com</t>
+          <t>khomyakisay@gmail.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -985,17 +985,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mandar</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Kretschmann</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mandar1921@yahoo.co.in</t>
+          <t>natekretschmann@gmail.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1007,17 +1007,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kristin</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ward</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kwardrmt@gmail.com</t>
+          <t>thomaskclee@gmail.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1029,17 +1029,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bogert</t>
+          <t>Gilley</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>bogertja@gmail.com</t>
+          <t>jason.gilley@uoit.net</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1051,17 +1051,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Ruth</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Murphy</t>
+          <t>Hoang</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jmurphy@ironbridgeequity.com</t>
+          <t>ninjaroo@gmail.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Karin</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Paskulin</t>
+          <t>Damla</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>exowill1@rogers.com</t>
+          <t>karin_damla@hotmail.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1095,17 +1095,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kleur</t>
+          <t>Yuridia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Garcia</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>production@kleurvision.com</t>
+          <t>yuyiisxd@gmail.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1117,17 +1117,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Yip</t>
+          <t>Bains</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>rebeccca.yip14@gmail.com</t>
+          <t>sarah.bains.13@gmail.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1139,17 +1139,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kawshik</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Basak</t>
+          <t>Cohen</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>kawshik.basak96@gmail.com</t>
+          <t>aarongabrielcohen@gmail.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1161,17 +1161,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Henrietta</t>
+          <t>Yiyi</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tsui</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>henriettatsui@gmail.com</t>
+          <t>852949906@qq.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tang</t>
+          <t>Tillo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>tangm614@gmail.com</t>
+          <t>coachjohn@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1205,17 +1205,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Xiaohu</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>liuxiaohujacky@gmail.com</t>
+          <t>dave.nurse@ymail.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1227,17 +1227,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Adel</t>
+          <t>Annie</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Stavitsky</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>adelstav@gmail.com</t>
+          <t>alt.anemsgs@gmail.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1249,17 +1249,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kitty</t>
+          <t>Mandar</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>kchan27@yahoo.com</t>
+          <t>mandar1921@yahoo.co.in</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1271,17 +1271,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Leanne</t>
+          <t>Kristin</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Ward</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>leanne@pickleplexclub.ca</t>
+          <t>kwardrmt@gmail.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1293,17 +1293,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Joel</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Douglas</t>
+          <t>Bogert</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>joel.douglas123456789@gmail.com</t>
+          <t>bogertja@gmail.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1315,17 +1315,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Jessie</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mills</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>yorkmills@pickleplexclub.ca</t>
+          <t>jessie1230_18@hotmail.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Selina</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dale</t>
+          <t>Yang</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>matthew.dale@sympatico.ca</t>
+          <t>torontogood66@hotmail.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1359,17 +1359,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Heesun</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Choi</t>
+          <t>Murphy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>postaloutlet@hotmail.com</t>
+          <t>jmurphy@ironbridgeequity.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1381,17 +1381,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kremer</t>
+          <t>Paskulin</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>rachel.kremer@outlook.com</t>
+          <t>exowill1@rogers.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1403,17 +1403,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Kleur</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mignotte</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>acm.milan.m@gmail.com</t>
+          <t>production@kleurvision.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1425,17 +1425,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Hoang</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>brianwlee17@gmail.com</t>
+          <t>adamahoang@gmail.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1447,17 +1447,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Shaun</t>
+          <t>Rebecca</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Linsao</t>
+          <t>Yip</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>shaun@pickleplexclub.ca</t>
+          <t>rebeccca.yip14@gmail.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1469,15 +1469,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Shirley</t>
+          <t>Kawshik</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lee</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>Basak</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>kawshik.basak96@gmail.com</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1487,15 +1491,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Congcong</t>
+          <t>Henrietta</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>Tsui</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>henriettatsui@gmail.com</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1505,15 +1513,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Navneet</t>
+          <t>xian</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bal</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>zhong</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>zhongxian.editor@gmail.com</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1523,15 +1535,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Scott</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>Tang</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>tangm614@gmail.com</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1541,15 +1557,19 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Xiaohu</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>liuxiaohujacky@gmail.com</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1559,15 +1579,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Shilpa</t>
+          <t>Adel</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pal</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>Stavitsky</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>adelstav@gmail.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1577,15 +1601,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Woo</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>hexiao.wang@outlook.com</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1595,15 +1623,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Kitty</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>kchan27@yahoo.com</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1613,15 +1645,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Allyano</t>
+          <t>Philseok</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Badrie-Deen</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>Han</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>irreversible0503@gmail.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1631,15 +1667,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Leanne</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>leanne@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1649,15 +1689,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Royce</t>
+          <t>Simon</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>Chun</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>simonhychun@gmail.com</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1667,15 +1711,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jiyaan</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Shukla</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>Douglas</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>joel.douglas123456789@gmail.com</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1685,15 +1733,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Lai Ming</t>
+          <t>York</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kwan</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>Mills</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1703,15 +1755,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Chapman</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ma</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>Dale</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>matthew.dale@sympatico.ca</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1721,15 +1777,19 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Dezhong</t>
+          <t>Heesun</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chen</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>Choi</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>postaloutlet@hotmail.com</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1739,15 +1799,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Myles</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Romero</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>Kremer</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>rachel.kremer@outlook.com</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1757,15 +1821,19 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Bernard</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chan</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>Mignotte</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>acm.milan.m@gmail.com</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1775,15 +1843,19 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ching</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>brianwlee17@gmail.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1793,15 +1865,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Ponny</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Popik</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>Wo</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ponnywo@yahoo.com</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1811,15 +1887,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Shaun</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cohen</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>Linsao</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>shaun@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1829,15 +1909,19 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>christian daryl</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jivov</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>juarez</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>christiandarylj25@gmail.com</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1847,12 +1931,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Dyllan</t>
+          <t>Shirley</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Opinaldo</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1865,12 +1949,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Malcolm</t>
+          <t>Congcong</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Beach</t>
+          <t>Zhang</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1883,12 +1967,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Noime</t>
+          <t>Navneet</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Manalo</t>
+          <t>Bal</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1901,12 +1985,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nixon</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1919,12 +2003,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Jayden</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Woo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1937,12 +2021,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ellen</t>
+          <t>Shilpa</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kurtz-Cohen</t>
+          <t>Pal</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1955,12 +2039,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ridley</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tsui</t>
+          <t>Woo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1973,12 +2057,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Yang</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1991,12 +2075,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Johnnie</t>
+          <t>Allyano</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>Badrie-Deen</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -2009,12 +2093,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Leveson</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -2027,12 +2111,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Abigail</t>
+          <t>Royce</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -2045,12 +2129,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sidney</t>
+          <t>Jiyaan</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Shukla</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -2063,12 +2147,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Wojtek</t>
+          <t>Lai Ming</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Kwan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -2081,12 +2165,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Geoff</t>
+          <t>Chapman</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Anderton</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2099,12 +2183,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Addy</t>
+          <t>Dezhong</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -2117,12 +2201,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Maxwell</t>
+          <t>Myles</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Leveson</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2135,12 +2219,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Bernard</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Du</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2153,12 +2237,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Ching</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -2171,12 +2255,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Beach</t>
+          <t>Popik</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2189,12 +2273,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Reid</t>
+          <t>Cohen</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -2207,12 +2291,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Maya</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Jivov</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2225,12 +2309,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Mathis</t>
+          <t>Dyllan</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Leveson</t>
+          <t>Opinaldo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -2243,12 +2327,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Malcolm</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Beach</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -2261,12 +2345,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Gavin</t>
+          <t>Noime</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tsui</t>
+          <t>Manalo</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2279,12 +2363,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Goertz</t>
+          <t>Nixon</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2297,12 +2381,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Ryab</t>
+          <t>Jayden</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bolger</t>
+          <t>Woo</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2315,12 +2399,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Lainey</t>
+          <t>Ellen</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Kurtz-Cohen</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2333,12 +2417,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Ridley</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bolger</t>
+          <t>Tsui</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2351,12 +2435,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Aceto</t>
+          <t>Yang</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -2369,12 +2453,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Johnnie</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Yin</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -2387,12 +2471,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Leveson</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2405,12 +2489,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Agnes</t>
+          <t>Abigail</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tong</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -2423,12 +2507,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Michael A</t>
+          <t>Sidney</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Popik</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -2441,12 +2525,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Matteo</t>
+          <t>Wojtek</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Zilli</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -2459,12 +2543,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Gwen</t>
+          <t>Geoff</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Chasson</t>
+          <t>Anderton</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -2477,12 +2561,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ankur</t>
+          <t>Addy</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kulshrestha</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2495,12 +2579,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>Maxwell</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Jivov</t>
+          <t>Leveson</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2513,12 +2597,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Du</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2531,12 +2615,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Chasson</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2549,12 +2633,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Ruchira</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Roy</t>
+          <t>Beach</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2567,12 +2651,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sulkowski</t>
+          <t>Reid</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2585,7 +2669,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Brent</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2603,12 +2687,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Mathis</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Aceto</t>
+          <t>Leveson</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2621,12 +2705,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ray</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cao</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2639,12 +2723,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sulkowski</t>
+          <t>Tsui</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2657,12 +2741,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>hunter</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>julien-dolphin</t>
+          <t>Goertz</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2675,12 +2759,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Ryab</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Bolger</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2693,12 +2777,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Milad</t>
+          <t>Lainey</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Modir</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2711,12 +2795,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Brandon Scott</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>Bolger</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2729,7 +2813,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2747,12 +2831,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Yin</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2765,12 +2849,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2783,12 +2867,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Agnes</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Kung</t>
+          <t>Tong</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2801,12 +2885,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Lalique K Y</t>
+          <t>Michael A</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Popik</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2819,12 +2903,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Jimmy</t>
+          <t>Matteo</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Yu</t>
+          <t>Zilli</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2837,12 +2921,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Lathan</t>
+          <t>Gwen</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Solis</t>
+          <t>Chasson</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2855,12 +2939,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>Ankur</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Beach</t>
+          <t>Kulshrestha</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -2873,7 +2957,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2891,12 +2975,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Zou</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -2909,12 +2993,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Arlene</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FitzGerald</t>
+          <t>Chasson</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -2927,12 +3011,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sakura</t>
+          <t>Ruchira</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Shimada</t>
+          <t>Roy</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -2945,12 +3029,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Cedric</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Chasson</t>
+          <t>Sulkowski</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -2963,12 +3047,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Brent</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Popik</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -2981,12 +3065,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Adrian</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Aceto</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -2999,12 +3083,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Axel</t>
+          <t>Ray</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Cao</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -3017,12 +3101,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Joo</t>
+          <t>Sulkowski</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -3035,19 +3119,15 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Bryle</t>
+          <t>hunter</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Flores</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>brylefanshawe@gmail.com</t>
-        </is>
-      </c>
+          <t>julien-dolphin</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3057,12 +3137,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Mika</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -3075,19 +3155,15 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Amir</t>
+          <t>Milad</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Haniff</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>amirhaniff@hotmail.com</t>
-        </is>
-      </c>
+          <t>Modir</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3097,12 +3173,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Brandon Scott</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ho</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -3115,12 +3191,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Abuan</t>
+          <t>Aceto</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -3133,12 +3209,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Lane</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>O'Connor</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -3151,12 +3227,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Sevier</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -3169,19 +3245,15 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Hayk</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Oganesyan</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>haykogn@gmail.com</t>
-        </is>
-      </c>
+          <t>Kung</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3191,12 +3263,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Celica</t>
+          <t>Lalique K Y</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -3209,19 +3281,15 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Eluxni</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Kanesathas</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>eluxthas@icloud.com</t>
-        </is>
-      </c>
+          <t>Yu</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3231,12 +3299,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ronan</t>
+          <t>Lathan</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Solis</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -3249,12 +3317,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Dakota</t>
+          <t>Cadence</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Fernandes</t>
+          <t>Beach</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -3267,12 +3335,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Zabaneh</t>
+          <t>Jivov</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -3285,12 +3353,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Celine</t>
+          <t>Lu</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Zabaneh</t>
+          <t>Zou</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -3303,12 +3371,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Chanie</t>
+          <t>Arlene</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Yucor</t>
+          <t>FitzGerald</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -3321,12 +3389,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Raphael</t>
+          <t>Sakura</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Del Rosario</t>
+          <t>Shimada</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -3339,12 +3407,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Dario</t>
+          <t>Cedric</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Jamalzadeh</t>
+          <t>Chasson</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -3357,12 +3425,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>Popik</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -3375,17 +3443,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ali</t>
+          <t>wilson</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>karimi</t>
+          <t>zz</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>alikarimi1313@hotmail.com</t>
+          <t>wilson277@gmail.com</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3397,17 +3465,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Wade</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ritcey</t>
+          <t>Jung</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>sueritcey@gmail.com</t>
+          <t>wadejung@outlook.com</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3419,15 +3487,19 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Zaina</t>
+          <t>Wei</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Zabaneh</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr"/>
+          <t>Gu</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>weigu_weigu@yahoo.ca</t>
+        </is>
+      </c>
       <c r="D155" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3437,12 +3509,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Aria</t>
+          <t>Adrian</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Fernandes</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -3455,12 +3527,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Maggie</t>
+          <t>Axel</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Chiu</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -3473,12 +3545,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Nirmaljeet</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>Joo</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -3491,17 +3563,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Brian J</t>
+          <t>Bryle</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Quinlan</t>
+          <t>Flores</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>brianquinlan@sympatico.ca</t>
+          <t>brylefanshawe@gmail.com</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3513,12 +3585,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>diana</t>
+          <t>Mika</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dodd</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -3531,15 +3603,19 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Amir</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr"/>
+          <t>Haniff</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>amirhaniff@hotmail.com</t>
+        </is>
+      </c>
       <c r="D161" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3549,15 +3625,19 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Emmanuel</t>
+          <t>Harvey</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Mendoza</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr"/>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>harveylee7355@gmail.com</t>
+        </is>
+      </c>
       <c r="D162" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3567,12 +3647,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Ashley</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Ho</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -3585,12 +3665,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Jasmine</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Xiao</t>
+          <t>Abuan</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -3603,12 +3683,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Bruce</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>O'Connor</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3621,12 +3701,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STEVEN</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Sevier</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -3639,15 +3719,19 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>Hayk</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Yang</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr"/>
+          <t>Oganesyan</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>haykogn@gmail.com</t>
+        </is>
+      </c>
       <c r="D167" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3657,12 +3741,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Janina</t>
+          <t>Celica</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>KLOPSCH</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -3675,17 +3759,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Eluxni</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Easey</t>
+          <t>Kanesathas</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>jenroberts6@gmail.com</t>
+          <t>eluxthas@icloud.com</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -3697,15 +3781,19 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Shilpa</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Young</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
+          <t>Sequeira</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ssequeira@gmail.com</t>
+        </is>
+      </c>
       <c r="D170" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3715,12 +3803,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Hendrik</t>
+          <t>Ronan</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>VanderMeulen</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -3733,12 +3821,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Justus</t>
+          <t>Dakota</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Fernandes</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -3751,12 +3839,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Zabaneh</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -3769,12 +3857,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Esther</t>
+          <t>Celine</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Zabaneh</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -3787,12 +3875,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Tammie</t>
+          <t>Chanie</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Fong</t>
+          <t>Yucor</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -3805,12 +3893,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Raphael</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Yin</t>
+          <t>Del Rosario</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -3823,12 +3911,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Dario</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Bennett</t>
+          <t>Jamalzadeh</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -3841,12 +3929,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Macdonald</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -3859,15 +3947,19 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Suhanee</t>
+          <t>ali</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Sood</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr"/>
+          <t>karimi</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>alikarimi1313@hotmail.com</t>
+        </is>
+      </c>
       <c r="D179" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3877,15 +3969,19 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Mylo</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Cotton</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr"/>
+          <t>Ritcey</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>sueritcey@gmail.com</t>
+        </is>
+      </c>
       <c r="D180" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3895,19 +3991,15 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Zaina</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Couse</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>jcouse@segalgcse.com</t>
-        </is>
-      </c>
+          <t>Zabaneh</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3917,12 +4009,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Josiah</t>
+          <t>Aria</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Fernandes</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -3935,12 +4027,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Maggie</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Aceto</t>
+          <t>Chiu</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -3953,12 +4045,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Brad</t>
+          <t>Nirmaljeet</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -3971,15 +4063,19 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Brian J</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Cotton</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr"/>
+          <t>Quinlan</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>brianquinlan@sympatico.ca</t>
+        </is>
+      </c>
       <c r="D185" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3989,12 +4085,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Vic</t>
+          <t>diana</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Suan</t>
+          <t>Dodd</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4007,19 +4103,15 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Cummings</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>mwcummings@hotmail.ca</t>
-        </is>
-      </c>
+          <t>Wong</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4029,12 +4121,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Hua</t>
+          <t>Emmanuel</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Shi</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4047,12 +4139,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Gila</t>
+          <t>Ashley</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Kohen Rydlewicz</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -4065,12 +4157,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Jasmine</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Aceto</t>
+          <t>Xiao</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -4083,12 +4175,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Care</t>
+          <t>Bruce</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Dodd</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -4101,12 +4193,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Godfrey</t>
+          <t>STEVEN</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Yeung</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -4119,19 +4211,15 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>claudine</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Lukawesky</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>davidclaudie@sympatico.ca</t>
-        </is>
-      </c>
+          <t>Yang</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4141,12 +4229,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Janina</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Suan</t>
+          <t>KLOPSCH</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -4159,15 +4247,19 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
+          <t>Easey</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>jenroberts6@gmail.com</t>
+        </is>
+      </c>
       <c r="D195" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4177,12 +4269,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Kieran</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Lai</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4195,19 +4287,15 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Hafsa</t>
+          <t>Hendrik</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Esmail</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>admin@powerofwordsacademy.ca</t>
-        </is>
-      </c>
+          <t>VanderMeulen</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4217,12 +4305,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Darryl</t>
+          <t>Justus</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Fortes</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -4235,12 +4323,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Henrietta</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Tsui</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -4253,12 +4341,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Esther</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Simunovic</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -4271,12 +4359,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Cole</t>
+          <t>Tammie</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Billinkoff</t>
+          <t>Fong</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -4289,12 +4377,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Bobby</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Cancelli</t>
+          <t>Yin</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -4307,12 +4395,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Jake</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Billinkoff</t>
+          <t>Bennett</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -4325,12 +4413,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Jennie</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Mohabir</t>
+          <t>Macdonald</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -4343,12 +4431,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Rachelle</t>
+          <t>Suhanee</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Sood</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -4361,12 +4449,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Mylo</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Girard</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -4379,17 +4467,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Natan</t>
+          <t>Couse</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>lior797@gmail.com</t>
+          <t>jcouse@segalgcse.com</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4401,12 +4489,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Kathleen</t>
+          <t>Josiah</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Nadon</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -4419,12 +4507,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Nadon</t>
+          <t>Aceto</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -4437,12 +4525,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Teos</t>
+          <t>Brad</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Vaccaro</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -4455,12 +4543,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Jackie</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -4473,12 +4561,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Jisoo</t>
+          <t>Vic</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Maynard</t>
+          <t>Suan</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -4496,10 +4584,14 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Karam</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr"/>
+          <t>Cummings</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>mwcummings@hotmail.ca</t>
+        </is>
+      </c>
       <c r="D213" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4509,12 +4601,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Hua</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Almaria</t>
+          <t>Shi</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -4527,12 +4619,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Sisily</t>
+          <t>Gila</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Solis</t>
+          <t>Kohen Rydlewicz</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -4545,12 +4637,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Lilybeth</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Solis</t>
+          <t>Aceto</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -4563,12 +4655,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Teos</t>
+          <t>Care</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Vaccaro</t>
+          <t>Dodd</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -4581,12 +4673,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Ksenia</t>
+          <t>Godfrey</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Vaccaro</t>
+          <t>Yeung</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -4599,15 +4691,19 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>claudine</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Nicholl</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr"/>
+          <t>Lukawesky</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>davidclaudie@sympatico.ca</t>
+        </is>
+      </c>
       <c r="D219" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4617,12 +4713,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Nicholl</t>
+          <t>Suan</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -4635,12 +4731,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Tay</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -4653,12 +4749,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Asllan</t>
+          <t>Kieran</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Lai</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -4671,15 +4767,19 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Giselle</t>
+          <t>Hafsa</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Del Rosario</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr"/>
+          <t>Esmail</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>admin@powerofwordsacademy.ca</t>
+        </is>
+      </c>
       <c r="D223" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4689,12 +4789,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Darryl</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Jenkins</t>
+          <t>Fortes</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -4707,12 +4807,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Henrietta</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Chin</t>
+          <t>Tsui</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -4725,12 +4825,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Cheung</t>
+          <t>Simunovic</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -4743,12 +4843,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Kiara</t>
+          <t>Cole</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Bici</t>
+          <t>Billinkoff</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -4761,12 +4861,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Bobby</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jin</t>
+          <t>Cancelli</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -4779,12 +4879,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Vicky</t>
+          <t>Jake</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Su</t>
+          <t>Billinkoff</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -4797,12 +4897,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Jennie</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Pileggi</t>
+          <t>Mohabir</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -4815,12 +4915,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Fiona</t>
+          <t>Rachelle</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -4833,12 +4933,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Brittany</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Horan</t>
+          <t>Girard</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -4851,15 +4951,19 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Folletet</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr"/>
+          <t>Natan</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>lior797@gmail.com</t>
+        </is>
+      </c>
       <c r="D233" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4869,12 +4973,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Ruchira</t>
+          <t>Kathleen</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Kulkarni</t>
+          <t>Nadon</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -4887,12 +4991,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Annie</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Tran</t>
+          <t>Nadon</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -4905,12 +5009,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Lilian</t>
+          <t>Teos</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Jiang</t>
+          <t>Vaccaro</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -4923,12 +5027,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Jackie</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -4941,12 +5045,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Pamela</t>
+          <t>Jisoo</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Ip</t>
+          <t>Maynard</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -4959,15 +5063,19 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Dana</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Ma</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr"/>
+          <t>Kwong</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>331.kwong@gmail.com</t>
+        </is>
+      </c>
       <c r="D239" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4977,12 +5085,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Kitt</t>
+          <t>Karam</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -4995,12 +5103,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Mack</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Lapointe</t>
+          <t>Almaria</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -5013,19 +5121,15 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Jay</t>
+          <t>Sisily</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Latiff</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>jaythefungi@proton.me</t>
-        </is>
-      </c>
+          <t>Solis</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5035,12 +5139,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Lin</t>
+          <t>Lilybeth</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>Solis</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -5053,12 +5157,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Mikhael</t>
+          <t>Teos</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>Vaccaro</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -5071,12 +5175,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Anh</t>
+          <t>Ksenia</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Vaccaro</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -5089,12 +5193,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Cheung</t>
+          <t>Nicholl</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -5107,19 +5211,15 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Liza</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Benkovitch</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>liza@d8teclub.com</t>
-        </is>
-      </c>
+          <t>Nicholl</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5129,12 +5229,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Patricio</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Dávalos ucha</t>
+          <t>Tay</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -5147,19 +5247,15 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Asllan</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Rodrigues</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>nrodrigues@cihi.ca</t>
-        </is>
-      </c>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5169,12 +5265,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Duy</t>
+          <t>Giselle</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Ho</t>
+          <t>Del Rosario</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -5187,12 +5283,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Nasim</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Hashemi</t>
+          <t>Jenkins</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -5205,12 +5301,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Ashley</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Vu</t>
+          <t>Chin</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -5223,12 +5319,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Dong</t>
+          <t>Cheung</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -5241,12 +5337,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Daisy</t>
+          <t>Kiara</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Xu</t>
+          <t>Bici</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -5259,12 +5355,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Kat</t>
+          <t>Jin</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -5277,19 +5373,15 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Vicky</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Bhamra</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>simranb1395@gmail.com</t>
-        </is>
-      </c>
+          <t>Su</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5299,12 +5391,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Shikha</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Kothari</t>
+          <t>Pileggi</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -5317,12 +5409,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Fiona</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Timosa</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -5335,12 +5427,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Brittany</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Davis</t>
+          <t>Horan</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -5353,12 +5445,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Hsieh</t>
+          <t>Folletet</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -5371,19 +5463,15 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>Ruchira</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Ko</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>rebecca.ko@jig.to</t>
-        </is>
-      </c>
+          <t>Kulkarni</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5393,19 +5481,15 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Urvashi</t>
+          <t>Annie</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Chauhan</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>urvashi.chauhan@clearscore.com</t>
-        </is>
-      </c>
+          <t>Tran</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5415,12 +5499,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Bryan</t>
+          <t>Lilian</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Jiang</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -5433,19 +5517,15 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Chi</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Quach</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>mesamune@hotmail.com</t>
-        </is>
-      </c>
+          <t>Lam</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5455,12 +5535,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Pamela</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Del rosario</t>
+          <t>Ip</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -5473,15 +5553,19 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Cooney</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr"/>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>samherson@hotmail.com</t>
+        </is>
+      </c>
       <c r="D266" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5491,12 +5575,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Galina</t>
+          <t>Dana</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Lad</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -5509,15 +5593,19 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Liam</t>
+          <t>Reah Angelee</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Cooney</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr"/>
+          <t>Saldivar</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>reahangeleesldvr@yahoo.com</t>
+        </is>
+      </c>
       <c r="D268" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5527,12 +5615,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Sahar</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Kitt</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -5545,15 +5633,19 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Arav</t>
+          <t>Andy</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr"/>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>andydnguyen92@gmail.com</t>
+        </is>
+      </c>
       <c r="D270" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5563,12 +5655,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Salama</t>
+          <t>Mack</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Karim</t>
+          <t>Lapointe</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -5581,15 +5673,19 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Jay</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Williams</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr"/>
+          <t>Latiff</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>jaythefungi@proton.me</t>
+        </is>
+      </c>
       <c r="D272" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5599,12 +5695,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Bryan</t>
+          <t>Lin</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Lu</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -5617,12 +5713,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Nix</t>
+          <t>Mikhael</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Cochangco</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -5635,12 +5731,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Lukas</t>
+          <t>Anh</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Szczurowski</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -5653,12 +5749,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Malks</t>
+          <t>Cheung</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -5671,15 +5767,19 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Miles</t>
+          <t>Liza</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Malks</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr"/>
+          <t>Benkovitch</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>liza@d8teclub.com</t>
+        </is>
+      </c>
       <c r="D277" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5689,12 +5789,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Kaitlyn</t>
+          <t>Patricio</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Dávalos ucha</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -5707,16 +5807,1904 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
+          <t>christopher</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Go Bio</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>pilyo311@gmail.com</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Kristy</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>kristysuen23@gmail.com</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Rodrigues</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>nrodrigues@cihi.ca</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Duy</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Ho</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Nasim</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Hashemi</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Cui</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>everydayisgreat777@gmail.com</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Ashley</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Vu</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Dong</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Daisy</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Xu</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Kat</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Bhamra</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>simranb1395@gmail.com</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Prince Xieder</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Tinguha</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>skylartheunis@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Shikha</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Kothari</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Prags</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Manickam</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>pragcan96@gmail.com</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Kate</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Kom</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>katekim@live.com</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Tracy</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Timosa</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Davis</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Hsieh</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Rebecca</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Ko</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>rebecca.ko@jig.to</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Urvashi</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Chauhan</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>urvashi.chauhan@clearscore.com</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Chi</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Quach</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>mesamune@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Del rosario</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Sumati</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>sumati.singh@outlook.com</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Cooney</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Galina</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Lad</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Cooney</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Sahar</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Arav</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Salama</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Karim</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Nix</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Cochangco</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Sharon</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Yang</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>sharon.ca@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Lukas</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Szczurowski</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Malks</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Malks</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Kaitlyn</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
           <t>Justin</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
+      <c r="B317" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr"/>
-      <c r="D279" t="inlineStr">
+      <c r="C317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Carly</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Handler</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>handlerc97@gmail.com</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Vinay</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Amarnani</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>vinay.amarnani1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>alan</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>tsang</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>altsanghk@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Tiffany</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>untitled.tif@gmail.com</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Ingrid</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Suhardja</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Shivangi</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Garg</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>canada.sgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Poling</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Pan</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>poling.pan0319@gmail.com</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Siya</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Garg</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>siyagarg.canada@gmail.com</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Mahir</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Shaikh</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>mahirthebest95@gmail.com</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Shayan</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Abbasi</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>abbasi.shayan1995@gmail.com</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>kHUSHAAN</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Garg</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Elliot</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Bhamani</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>elliot.bhamani@gmail.com</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Danielle</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Catania</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>catania.danielle@gmail.com</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Amir</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Nouraein</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>parhamnuri@gmail.com</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Vania</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Garg</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Kit</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Yiu</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>hungkityiu@gmail.com</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Simom</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Yim</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Emmy</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>emmy.cao@zoocasa.com</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Hanny</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Chau</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>hanny.chau@outlook.com</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Nestico</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>thomasjamesnestico@gmail.com</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Logan</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Chau</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Chau</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Ishaan</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Mehta</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>mehtaishaan4@gmail.com</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Zimo</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>King</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>utgw01@gmail.com</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Terry</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>jiaxiangw0@gmail.com</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>arjun</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>kapur</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>arjun.ak67@gmail.com</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Henry</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>heinhtet1995@gmail.com</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Bonnie</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Lam</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>blam@cihi.ca</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>linda33440@gmail.com</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Yang</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>michael_yang@live.com</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Jasmine</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Huang</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>qiuminhuang@gmail.com</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Zhenzhen</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>wzzheloise@gmail.com</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Wesley</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Lin</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>wesley.linvan@gmail.com</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Nischaye</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Ramparsad</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>nischaye05@gmail.com</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Tiffany</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Yiu</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>tiff.y7281@gmail.com</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Shuqin</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Xia</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>525160331@qq.com</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>jun</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>ji</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>wilson277@live.com</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Mehar</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Nakai</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>meharnakai@gmail.com</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Riley</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Rob</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>McKee</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>robertmckee286@gmail.com</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Xianming</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Zhu</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>xianmingzhu@gmail.com</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Jasmine</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Huang</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Wei</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Hou</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>weihou99@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Andrews</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>ewandrews@bell.net</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Claire</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Gregorio</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>claire.gregorio512@gmail.com</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Joeeph</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Atkinson-Orlando</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>josephao@rogers.com</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Debahuti</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Basu</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>debahuti@gmail.com</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>bryanchen2013@gmail.com</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Turner</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>johnt.xaos@gmail.com</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>BIN</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>WANG</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>binwcs@gmail.com</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Shirley</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>shirleyc2020.2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Varun</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Sondhi</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>sondhi.varun@gmail.com</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>markdavidrose0@gmail.com</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
         </is>

--- a/docs/downloads/York_Mills.xlsx
+++ b/docs/downloads/York_Mills.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D371"/>
+  <dimension ref="A1:D377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6025,19 +6025,15 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Prince Xieder</t>
+          <t>Shikha</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Tinguha</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>skylartheunis@yahoo.com</t>
-        </is>
-      </c>
+          <t>Kothari</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6047,15 +6043,19 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Shikha</t>
+          <t>Prags</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Kothari</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr"/>
+          <t>Manickam</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>pragcan96@gmail.com</t>
+        </is>
+      </c>
       <c r="D291" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6065,17 +6065,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Prags</t>
+          <t>Kate</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Manickam</t>
+          <t>Kom</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>pragcan96@gmail.com</t>
+          <t>katekim@live.com</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -6087,19 +6087,15 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Kate</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Kom</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>katekim@live.com</t>
-        </is>
-      </c>
+          <t>Timosa</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6109,12 +6105,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Timosa</t>
+          <t>Davis</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -6127,12 +6123,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Davis</t>
+          <t>Hsieh</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -6145,15 +6141,19 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Rebecca</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Hsieh</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr"/>
+          <t>Ko</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>rebecca.ko@jig.to</t>
+        </is>
+      </c>
       <c r="D296" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6163,17 +6163,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>Urvashi</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Ko</t>
+          <t>Chauhan</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>rebecca.ko@jig.to</t>
+          <t>urvashi.chauhan@clearscore.com</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -6185,19 +6185,15 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Urvashi</t>
+          <t>Bryan</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Chauhan</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>urvashi.chauhan@clearscore.com</t>
-        </is>
-      </c>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6207,15 +6203,19 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Bryan</t>
+          <t>Chi</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Nguyen</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr"/>
+          <t>Quach</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>mesamune@hotmail.com</t>
+        </is>
+      </c>
       <c r="D299" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6225,19 +6225,15 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Chi</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Quach</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>mesamune@hotmail.com</t>
-        </is>
-      </c>
+          <t>Del rosario</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6247,15 +6243,19 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Sumati</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Del rosario</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr"/>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>sumati.singh@outlook.com</t>
+        </is>
+      </c>
       <c r="D301" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6265,19 +6265,15 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Sumati</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Singh</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>sumati.singh@outlook.com</t>
-        </is>
-      </c>
+          <t>Cooney</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6287,12 +6283,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Galina</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Cooney</t>
+          <t>Lad</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -6305,12 +6301,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Galina</t>
+          <t>Liam</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Lad</t>
+          <t>Cooney</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
@@ -6323,12 +6319,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Liam</t>
+          <t>Sahar</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Cooney</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
@@ -6341,7 +6337,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Sahar</t>
+          <t>Arav</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -6359,12 +6355,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Arav</t>
+          <t>Salama</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Karim</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -6377,12 +6373,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Salama</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Karim</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
@@ -6395,12 +6391,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Bryan</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -6413,12 +6409,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Bryan</t>
+          <t>Nix</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Cochangco</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
@@ -6431,15 +6427,19 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Nix</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Cochangco</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr"/>
+          <t>Yang</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>sharon.ca@hotmail.com</t>
+        </is>
+      </c>
       <c r="D311" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6449,19 +6449,15 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Lukas</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Yang</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>sharon.ca@hotmail.com</t>
-        </is>
-      </c>
+          <t>Szczurowski</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6471,12 +6467,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Lukas</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Szczurowski</t>
+          <t>Malks</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -6489,7 +6485,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Miles</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -6507,12 +6503,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Miles</t>
+          <t>Kaitlyn</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Malks</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -6525,7 +6521,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Kaitlyn</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -6543,15 +6539,19 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Carly</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr"/>
+          <t>Handler</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>handlerc97@gmail.com</t>
+        </is>
+      </c>
       <c r="D317" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6561,17 +6561,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Carly</t>
+          <t>Vinay</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Handler</t>
+          <t>Amarnani</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>handlerc97@gmail.com</t>
+          <t>vinay.amarnani1@gmail.com</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -6583,17 +6583,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Vinay</t>
+          <t>alan</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Amarnani</t>
+          <t>tsang</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>vinay.amarnani1@gmail.com</t>
+          <t>altsanghk@hotmail.com</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -6605,17 +6605,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>alan</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>tsang</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>altsanghk@hotmail.com</t>
+          <t>untitled.tif@gmail.com</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -6627,19 +6627,15 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>Ingrid</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>untitled.tif@gmail.com</t>
-        </is>
-      </c>
+          <t>Suhardja</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6649,15 +6645,19 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Ingrid</t>
+          <t>Shivangi</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Suhardja</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr"/>
+          <t>Garg</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>canada.sgarg@gmail.com</t>
+        </is>
+      </c>
       <c r="D322" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6667,17 +6667,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Shivangi</t>
+          <t>Poling</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Garg</t>
+          <t>Pan</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>canada.sgarg@gmail.com</t>
+          <t>poling.pan0319@gmail.com</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -6689,17 +6689,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Poling</t>
+          <t>Siya</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Pan</t>
+          <t>Garg</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>poling.pan0319@gmail.com</t>
+          <t>siyagarg.canada@gmail.com</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -6711,17 +6711,17 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Siya</t>
+          <t>Mahir</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Garg</t>
+          <t>Shaikh</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>siyagarg.canada@gmail.com</t>
+          <t>mahirthebest95@gmail.com</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -6733,17 +6733,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Mahir</t>
+          <t>Shayan</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Shaikh</t>
+          <t>Abbasi</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>mahirthebest95@gmail.com</t>
+          <t>abbasi.shayan1995@gmail.com</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -6755,19 +6755,15 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Shayan</t>
+          <t>kHUSHAAN</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Abbasi</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>abbasi.shayan1995@gmail.com</t>
-        </is>
-      </c>
+          <t>Garg</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6777,15 +6773,19 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>kHUSHAAN</t>
+          <t>Elliot</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Garg</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr"/>
+          <t>Bhamani</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>elliot.bhamani@gmail.com</t>
+        </is>
+      </c>
       <c r="D328" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6795,17 +6795,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Elliot</t>
+          <t>Danielle</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Bhamani</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>elliot.bhamani@gmail.com</t>
+          <t>catania.danielle@gmail.com</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -6817,17 +6817,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Danielle</t>
+          <t>Amir</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Nouraein</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>catania.danielle@gmail.com</t>
+          <t>parhamnuri@gmail.com</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -6839,19 +6839,15 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Amir</t>
+          <t>Vania</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Nouraein</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>parhamnuri@gmail.com</t>
-        </is>
-      </c>
+          <t>Garg</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6861,15 +6857,19 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Vania</t>
+          <t>Kit</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Garg</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
+          <t>Yiu</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>hungkityiu@gmail.com</t>
+        </is>
+      </c>
       <c r="D332" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6879,19 +6879,15 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Kit</t>
+          <t>Simom</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Yiu</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>hungkityiu@gmail.com</t>
-        </is>
-      </c>
+          <t>Yim</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6901,15 +6897,19 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Simom</t>
+          <t>Emmy</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Yim</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>emmy.cao@zoocasa.com</t>
+        </is>
+      </c>
       <c r="D334" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6919,17 +6919,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Emmy</t>
+          <t>Hanny</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Cao</t>
+          <t>Chau</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>emmy.cao@zoocasa.com</t>
+          <t>hanny.chau@outlook.com</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -6941,17 +6941,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Hanny</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Chau</t>
+          <t>Nestico</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>hanny.chau@outlook.com</t>
+          <t>thomasjamesnestico@gmail.com</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -6963,19 +6963,15 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Nestico</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>thomasjamesnestico@gmail.com</t>
-        </is>
-      </c>
+          <t>Chau</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6985,7 +6981,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Tyler</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -7003,15 +6999,19 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Ishaan</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Chau</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr"/>
+          <t>Mehta</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>mehtaishaan4@gmail.com</t>
+        </is>
+      </c>
       <c r="D339" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7021,19 +7021,15 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Ishaan</t>
+          <t>Zimo</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Mehta</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>mehtaishaan4@gmail.com</t>
-        </is>
-      </c>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7043,15 +7039,19 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Zimo</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Chen</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr"/>
+          <t>King</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>utgw01@gmail.com</t>
+        </is>
+      </c>
       <c r="D341" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7061,17 +7061,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Terry</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>utgw01@gmail.com</t>
+          <t>jiaxiangw0@gmail.com</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -7083,17 +7083,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Terry</t>
+          <t>arjun</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>kapur</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>jiaxiangw0@gmail.com</t>
+          <t>arjun.ak67@gmail.com</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -7105,17 +7105,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>arjun</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>kapur</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>arjun.ak67@gmail.com</t>
+          <t>heinhtet1995@gmail.com</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -7127,17 +7127,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Bonnie</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>heinhtet1995@gmail.com</t>
+          <t>blam@cihi.ca</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -7149,17 +7149,17 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Bonnie</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>blam@cihi.ca</t>
+          <t>linda33440@gmail.com</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -7171,17 +7171,17 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Yang</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>linda33440@gmail.com</t>
+          <t>michael_yang@live.com</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -7193,17 +7193,17 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Jasmine</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Yang</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>michael_yang@live.com</t>
+          <t>qiuminhuang@gmail.com</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -7215,17 +7215,17 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Jasmine</t>
+          <t>Zhenzhen</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>qiuminhuang@gmail.com</t>
+          <t>wzzheloise@gmail.com</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -7237,17 +7237,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Zhenzhen</t>
+          <t>Wesley</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Lin</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>wzzheloise@gmail.com</t>
+          <t>wesley.linvan@gmail.com</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -7259,17 +7259,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Wesley</t>
+          <t>Nischaye</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Lin</t>
+          <t>Ramparsad</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>wesley.linvan@gmail.com</t>
+          <t>nischaye05@gmail.com</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -7281,17 +7281,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Nischaye</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Ramparsad</t>
+          <t>Yiu</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>nischaye05@gmail.com</t>
+          <t>tiff.y7281@gmail.com</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -7303,17 +7303,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>Shuqin</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Yiu</t>
+          <t>Xia</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>tiff.y7281@gmail.com</t>
+          <t>525160331@qq.com</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -7325,17 +7325,17 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Shuqin</t>
+          <t>jun</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Xia</t>
+          <t>ji</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>525160331@qq.com</t>
+          <t>wilson277@live.com</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -7347,17 +7347,17 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>jun</t>
+          <t>Mehar</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>ji</t>
+          <t>Nakai</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>wilson277@live.com</t>
+          <t>meharnakai@gmail.com</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -7369,19 +7369,15 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Mehar</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Nakai</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>meharnakai@gmail.com</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7391,15 +7387,19 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Rob</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr"/>
+          <t>McKee</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>robertmckee286@gmail.com</t>
+        </is>
+      </c>
       <c r="D357" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7409,17 +7409,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>Xianming</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>McKee</t>
+          <t>Zhu</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>robertmckee286@gmail.com</t>
+          <t>xianmingzhu@gmail.com</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -7431,19 +7431,15 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Xianming</t>
+          <t>Jasmine</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Zhu</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>xianmingzhu@gmail.com</t>
-        </is>
-      </c>
+          <t>Huang</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7453,15 +7449,19 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Jasmine</t>
+          <t>Wei</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Huang</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr"/>
+          <t>Hou</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>weihou99@yahoo.com</t>
+        </is>
+      </c>
       <c r="D360" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7471,17 +7471,17 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Wei</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Hou</t>
+          <t>Andrews</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>weihou99@yahoo.com</t>
+          <t>ewandrews@bell.net</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -7493,17 +7493,17 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Claire</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Andrews</t>
+          <t>Gregorio</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>ewandrews@bell.net</t>
+          <t>claire.gregorio512@gmail.com</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -7515,17 +7515,17 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Claire</t>
+          <t>Joeeph</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Gregorio</t>
+          <t>Atkinson-Orlando</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>claire.gregorio512@gmail.com</t>
+          <t>josephao@rogers.com</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -7537,17 +7537,17 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Joeeph</t>
+          <t>Debahuti</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Atkinson-Orlando</t>
+          <t>Basu</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>josephao@rogers.com</t>
+          <t>debahuti@gmail.com</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -7559,17 +7559,17 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Debahuti</t>
+          <t>Bryan</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Basu</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>debahuti@gmail.com</t>
+          <t>bryanchen2013@gmail.com</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -7581,17 +7581,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Bryan</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>bryanchen2013@gmail.com</t>
+          <t>johnt.xaos@gmail.com</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -7603,17 +7603,17 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>BIN</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>WANG</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>johnt.xaos@gmail.com</t>
+          <t>binwcs@gmail.com</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -7625,17 +7625,17 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>BIN</t>
+          <t>Shirley</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>WANG</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>binwcs@gmail.com</t>
+          <t>shirleyc2020.2020@gmail.com</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -7647,17 +7647,17 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Shirley</t>
+          <t>Varun</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Sondhi</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>shirleyc2020.2020@gmail.com</t>
+          <t>sondhi.varun@gmail.com</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -7669,17 +7669,17 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Varun</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Sondhi</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>sondhi.varun@gmail.com</t>
+          <t>markdavidrose0@gmail.com</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -7691,20 +7691,152 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Dina</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Pantaleon</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>markdavidrose0@gmail.com</t>
+          <t>gotsoul27@gmail.com</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Hugo</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Tran</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>nismoboy1992@gmail.com</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Williamson</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>michaelrwilliamson2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Mayuresh</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Sawant</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>mayuresh.sawant@live.in</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Helen</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Im</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>helenim3@gmail.com</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Maroon</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>nicolemaroon@gmail.com</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Viada Marie</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Cauyao</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>viadamariecauyao2442@gmail.com</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
         </is>

--- a/docs/downloads/York_Mills.xlsx
+++ b/docs/downloads/York_Mills.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D377"/>
+  <dimension ref="A1:D411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1073,17 +1073,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Karin</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Damla</t>
+          <t>Chapman</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>karin_damla@hotmail.com</t>
+          <t>david.88.chapman@gmail.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1095,17 +1095,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Yuridia</t>
+          <t>Karin</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Garcia</t>
+          <t>Damla</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>yuyiisxd@gmail.com</t>
+          <t>karin_damla@hotmail.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1117,17 +1117,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Yuridia</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bains</t>
+          <t>Garcia</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sarah.bains.13@gmail.com</t>
+          <t>yuyiisxd@gmail.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1139,17 +1139,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cohen</t>
+          <t>Bains</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>aarongabrielcohen@gmail.com</t>
+          <t>sarah.bains.13@gmail.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1161,17 +1161,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Yiyi</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Cohen</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>852949906@qq.com</t>
+          <t>aarongabrielcohen@gmail.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Yiyi</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tillo</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>coachjohn@pickleplexclub.ca</t>
+          <t>852949906@qq.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1205,17 +1205,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Tillo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>dave.nurse@ymail.com</t>
+          <t>coachjohn@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1227,17 +1227,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Annie</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>alt.anemsgs@gmail.com</t>
+          <t>dave.nurse@ymail.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1249,17 +1249,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mandar</t>
+          <t>Annie</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>mandar1921@yahoo.co.in</t>
+          <t>alt.anemsgs@gmail.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1271,17 +1271,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kristin</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ward</t>
+          <t>Del Giudice</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>kwardrmt@gmail.com</t>
+          <t>dave@delgiudice.ca</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1293,17 +1293,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Mandar</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bogert</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>bogertja@gmail.com</t>
+          <t>mandar1921@yahoo.co.in</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1315,17 +1315,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jessie</t>
+          <t>Kristin</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Ward</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jessie1230_18@hotmail.com</t>
+          <t>kwardrmt@gmail.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Selina</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Yang</t>
+          <t>Bogert</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>torontogood66@hotmail.com</t>
+          <t>bogertja@gmail.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1359,17 +1359,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Jessie</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Murphy</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jmurphy@ironbridgeequity.com</t>
+          <t>jessie1230_18@hotmail.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1381,17 +1381,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Selina</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Paskulin</t>
+          <t>Yang</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>exowill1@rogers.com</t>
+          <t>torontogood66@hotmail.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1403,17 +1403,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kleur</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Murphy</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>production@kleurvision.com</t>
+          <t>jmurphy@ironbridgeequity.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1425,17 +1425,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Hoang</t>
+          <t>Paskulin</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>adamahoang@gmail.com</t>
+          <t>exowill1@rogers.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1447,17 +1447,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>Kleur</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Yip</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>rebeccca.yip14@gmail.com</t>
+          <t>production@kleurvision.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1469,17 +1469,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kawshik</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Basak</t>
+          <t>Hoang</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kawshik.basak96@gmail.com</t>
+          <t>adamahoang@gmail.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1491,17 +1491,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Henrietta</t>
+          <t>Rebecca</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tsui</t>
+          <t>Yip</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>henriettatsui@gmail.com</t>
+          <t>rebeccca.yip14@gmail.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1513,17 +1513,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>xian</t>
+          <t>Kawshik</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>zhong</t>
+          <t>Basak</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>zhongxian.editor@gmail.com</t>
+          <t>kawshik.basak96@gmail.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1535,17 +1535,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Henrietta</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tang</t>
+          <t>Tsui</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>tangm614@gmail.com</t>
+          <t>henriettatsui@gmail.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1557,17 +1557,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Xiaohu</t>
+          <t>xian</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>zhong</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>liuxiaohujacky@gmail.com</t>
+          <t>zhongxian.editor@gmail.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1579,17 +1579,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Adel</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Stavitsky</t>
+          <t>Tang</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>adelstav@gmail.com</t>
+          <t>tangm614@gmail.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1601,17 +1601,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Xiaohu</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>hexiao.wang@outlook.com</t>
+          <t>liuxiaohujacky@gmail.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1623,17 +1623,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kitty</t>
+          <t>Adel</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Stavitsky</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>kchan27@yahoo.com</t>
+          <t>adelstav@gmail.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1645,17 +1645,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Philseok</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Han</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>irreversible0503@gmail.com</t>
+          <t>hexiao.wang@outlook.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1667,17 +1667,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Leanne</t>
+          <t>Kitty</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>leanne@pickleplexclub.ca</t>
+          <t>kchan27@yahoo.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1689,17 +1689,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Philseok</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chun</t>
+          <t>Han</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>simonhychun@gmail.com</t>
+          <t>irreversible0503@gmail.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1711,17 +1711,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Joel</t>
+          <t>Leanne</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Douglas</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>joel.douglas123456789@gmail.com</t>
+          <t>leanne@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1733,17 +1733,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Simon</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mills</t>
+          <t>Chun</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>yorkmills@pickleplexclub.ca</t>
+          <t>simonhychun@gmail.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1755,17 +1755,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dale</t>
+          <t>Douglas</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>matthew.dale@sympatico.ca</t>
+          <t>joel.douglas123456789@gmail.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1777,17 +1777,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Heesun</t>
+          <t>York</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Choi</t>
+          <t>Mills</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>postaloutlet@hotmail.com</t>
+          <t>yorkmills@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1799,17 +1799,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kremer</t>
+          <t>Dale</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>rachel.kremer@outlook.com</t>
+          <t>matthew.dale@sympatico.ca</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1821,17 +1821,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mignotte</t>
+          <t>Lui</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>acm.milan.m@gmail.com</t>
+          <t>ltdeditionlis@gmail.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1843,17 +1843,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>Heesun</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Choi</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>brianwlee17@gmail.com</t>
+          <t>postaloutlet@hotmail.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1865,17 +1865,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ponny</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wo</t>
+          <t>Kremer</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ponnywo@yahoo.com</t>
+          <t>rachel.kremer@outlook.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1887,17 +1887,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Shaun</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Linsao</t>
+          <t>Mignotte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>shaun@pickleplexclub.ca</t>
+          <t>acm.milan.m@gmail.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1909,17 +1909,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>christian daryl</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>juarez</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>christiandarylj25@gmail.com</t>
+          <t>brianwlee17@gmail.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1931,15 +1931,19 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Shirley</t>
+          <t>Ponny</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Lee</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>Wo</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ponnywo@yahoo.com</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1949,15 +1953,19 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Congcong</t>
+          <t>Shaun</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>Linsao</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>shaun@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1967,15 +1975,19 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Navneet</t>
+          <t>christian daryl</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bal</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>juarez</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>christiandarylj25@gmail.com</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -1985,12 +1997,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>Shirley</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -2003,12 +2015,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Congcong</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Zhang</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -2021,12 +2033,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Shilpa</t>
+          <t>Navneet</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pal</t>
+          <t>Bal</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -2039,12 +2051,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Woo</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -2057,12 +2069,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -2075,12 +2087,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Allyano</t>
+          <t>Shilpa</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Badrie-Deen</t>
+          <t>Pal</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -2093,12 +2105,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Woo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -2111,12 +2123,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Royce</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -2129,12 +2141,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Jiyaan</t>
+          <t>Allyano</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Shukla</t>
+          <t>Badrie-Deen</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -2147,12 +2159,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Lai Ming</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kwan</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -2165,12 +2177,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Chapman</t>
+          <t>Royce</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2183,12 +2195,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Dezhong</t>
+          <t>Jiyaan</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Shukla</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -2201,12 +2213,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Myles</t>
+          <t>Lai Ming</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Romero</t>
+          <t>Kwan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2219,12 +2231,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Bernard</t>
+          <t>Chapman</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2237,12 +2249,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Dezhong</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ching</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -2255,12 +2267,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Myles</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Popik</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2273,12 +2285,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Bernard</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cohen</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -2291,12 +2303,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jivov</t>
+          <t>Ching</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2309,12 +2321,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Dyllan</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Opinaldo</t>
+          <t>Popik</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -2327,12 +2339,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Malcolm</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Beach</t>
+          <t>Cohen</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -2345,12 +2357,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Noime</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Manalo</t>
+          <t>Jivov</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2363,12 +2375,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Dyllan</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nixon</t>
+          <t>Opinaldo</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2381,12 +2393,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Jayden</t>
+          <t>Malcolm</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Woo</t>
+          <t>Beach</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2399,12 +2411,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ellen</t>
+          <t>Noime</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Kurtz-Cohen</t>
+          <t>Manalo</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2417,12 +2429,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ridley</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tsui</t>
+          <t>Nixon</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2435,12 +2447,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Jayden</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Yang</t>
+          <t>Woo</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -2453,12 +2465,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Johnnie</t>
+          <t>Ellen</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>Kurtz-Cohen</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -2471,12 +2483,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Ridley</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Leveson</t>
+          <t>Tsui</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2489,12 +2501,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Abigail</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Yang</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -2507,12 +2519,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sidney</t>
+          <t>Johnnie</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -2525,12 +2537,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Wojtek</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Leveson</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -2543,12 +2555,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Geoff</t>
+          <t>Abigail</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Anderton</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -2561,12 +2573,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Addy</t>
+          <t>Sidney</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2579,12 +2591,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Maxwell</t>
+          <t>Wojtek</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Leveson</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2597,12 +2609,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Geoff</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Du</t>
+          <t>Anderton</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2615,12 +2627,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Addy</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2633,12 +2645,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Maxwell</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Beach</t>
+          <t>Leveson</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2651,12 +2663,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Reid</t>
+          <t>Du</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2669,12 +2681,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Maya</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2687,12 +2699,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Mathis</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Leveson</t>
+          <t>Beach</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2705,12 +2717,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Reid</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2723,12 +2735,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Gavin</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tsui</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2741,12 +2753,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Mathis</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Goertz</t>
+          <t>Leveson</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2759,12 +2771,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ryab</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Bolger</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2777,12 +2789,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Lainey</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Tsui</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2795,12 +2807,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bolger</t>
+          <t>Goertz</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2813,12 +2825,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Ryab</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Aceto</t>
+          <t>Bolger</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2831,12 +2843,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Lainey</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Yin</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2849,12 +2861,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Bolger</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2867,12 +2879,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Agnes</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tong</t>
+          <t>Aceto</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2885,12 +2897,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Michael A</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Popik</t>
+          <t>Yin</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2903,12 +2915,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Matteo</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Zilli</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2921,12 +2933,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Gwen</t>
+          <t>Agnes</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Chasson</t>
+          <t>Tong</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2939,12 +2951,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Ankur</t>
+          <t>Michael A</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Kulshrestha</t>
+          <t>Popik</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -2957,12 +2969,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>Matteo</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Jivov</t>
+          <t>Zilli</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -2975,12 +2987,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Gwen</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Chasson</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -2993,12 +3005,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Ankur</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Chasson</t>
+          <t>Kulshrestha</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -3011,12 +3023,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ruchira</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Roy</t>
+          <t>Jivov</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -3029,12 +3041,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Sulkowski</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3047,12 +3059,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Brent</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Chasson</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -3065,12 +3077,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Ruchira</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Aceto</t>
+          <t>Roy</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -3083,12 +3095,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ray</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Cao</t>
+          <t>Sulkowski</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -3101,12 +3113,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Brent</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Sulkowski</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -3119,12 +3131,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>hunter</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>julien-dolphin</t>
+          <t>Aceto</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -3137,12 +3149,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Ray</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Cao</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -3155,12 +3167,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Milad</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Modir</t>
+          <t>Sulkowski</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -3173,12 +3185,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Brandon Scott</t>
+          <t>hunter</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>julien-dolphin</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -3191,12 +3203,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Aceto</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -3209,12 +3221,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Milad</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Modir</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -3227,12 +3239,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Brandon Scott</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -3245,12 +3257,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Kung</t>
+          <t>Aceto</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -3263,12 +3275,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Lalique K Y</t>
+          <t>Lane</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -3281,12 +3293,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Jimmy</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Yu</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -3299,12 +3311,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Lathan</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Solis</t>
+          <t>Kung</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -3317,12 +3329,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>Lalique K Y</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Beach</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -3335,12 +3347,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Jivov</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -3353,12 +3365,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>Lathan</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Zou</t>
+          <t>Solis</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -3371,12 +3383,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Arlene</t>
+          <t>Cadence</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>FitzGerald</t>
+          <t>Beach</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -3389,12 +3401,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sakura</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Shimada</t>
+          <t>Jivov</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -3407,12 +3419,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Cedric</t>
+          <t>Lu</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Chasson</t>
+          <t>Zou</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -3425,12 +3437,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Arlene</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Popik</t>
+          <t>FitzGerald</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -3443,19 +3455,15 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>wilson</t>
+          <t>Sakura</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>zz</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>wilson277@gmail.com</t>
-        </is>
-      </c>
+          <t>Shimada</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3465,19 +3473,15 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Wade</t>
+          <t>Cedric</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Jung</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>wadejung@outlook.com</t>
-        </is>
-      </c>
+          <t>Chasson</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3487,19 +3491,15 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Wei</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Gu</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>weigu_weigu@yahoo.ca</t>
-        </is>
-      </c>
+          <t>Popik</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3509,15 +3509,19 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Adrian</t>
+          <t>wilson</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Lee</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr"/>
+          <t>zz</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>wilson277@gmail.com</t>
+        </is>
+      </c>
       <c r="D156" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3527,15 +3531,19 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Axel</t>
+          <t>Wade</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Lee</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr"/>
+          <t>Jung</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>wadejung@outlook.com</t>
+        </is>
+      </c>
       <c r="D157" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3545,15 +3553,19 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Wei</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Joo</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr"/>
+          <t>Gu</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>weigu_weigu@yahoo.ca</t>
+        </is>
+      </c>
       <c r="D158" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3563,19 +3575,15 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Bryle</t>
+          <t>Adrian</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Flores</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>brylefanshawe@gmail.com</t>
-        </is>
-      </c>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3585,7 +3593,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Mika</t>
+          <t>Axel</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3603,19 +3611,15 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Amir</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Haniff</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>amirhaniff@hotmail.com</t>
-        </is>
-      </c>
+          <t>Joo</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3625,17 +3629,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Harvey</t>
+          <t>Bryle</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Flores</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>harveylee7355@gmail.com</t>
+          <t>brylefanshawe@gmail.com</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3647,12 +3651,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Mika</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Ho</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -3665,15 +3669,19 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Amir</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Abuan</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr"/>
+          <t>Haniff</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>amirhaniff@hotmail.com</t>
+        </is>
+      </c>
       <c r="D164" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3683,15 +3691,19 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Harvey</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>O'Connor</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr"/>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>harveylee7355@gmail.com</t>
+        </is>
+      </c>
       <c r="D165" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3701,15 +3713,19 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Ray</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Sevier</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr"/>
+          <t>hakami</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ray.hakami@gmail.com</t>
+        </is>
+      </c>
       <c r="D166" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3719,19 +3735,15 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Hayk</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Oganesyan</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>haykogn@gmail.com</t>
-        </is>
-      </c>
+          <t>Ho</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3741,12 +3753,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Celica</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Abuan</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -3759,19 +3771,15 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Eluxni</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Kanesathas</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>eluxthas@icloud.com</t>
-        </is>
-      </c>
+          <t>O'Connor</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3781,19 +3789,15 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Shilpa</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Sequeira</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>ssequeira@gmail.com</t>
-        </is>
-      </c>
+          <t>Sevier</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3803,15 +3807,19 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ronan</t>
+          <t>Hayk</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr"/>
+          <t>Oganesyan</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>haykogn@gmail.com</t>
+        </is>
+      </c>
       <c r="D171" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3821,12 +3829,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Dakota</t>
+          <t>Celica</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Fernandes</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -3839,15 +3847,19 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Eluxni</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Zabaneh</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr"/>
+          <t>Kanesathas</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>eluxthas@icloud.com</t>
+        </is>
+      </c>
       <c r="D173" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3857,15 +3869,19 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Celine</t>
+          <t>Shilpa</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Zabaneh</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr"/>
+          <t>Sequeira</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ssequeira@gmail.com</t>
+        </is>
+      </c>
       <c r="D174" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3875,12 +3891,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Chanie</t>
+          <t>Ronan</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Yucor</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -3893,12 +3909,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Raphael</t>
+          <t>Dakota</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Del Rosario</t>
+          <t>Fernandes</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -3911,12 +3927,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Dario</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Jamalzadeh</t>
+          <t>Zabaneh</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -3929,12 +3945,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Celine</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>Zabaneh</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -3947,19 +3963,15 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ali</t>
+          <t>Chanie</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>karimi</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>alikarimi1313@hotmail.com</t>
-        </is>
-      </c>
+          <t>Yucor</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3969,19 +3981,15 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Raphael</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ritcey</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>sueritcey@gmail.com</t>
-        </is>
-      </c>
+          <t>Del Rosario</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -3991,12 +3999,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Zaina</t>
+          <t>Dario</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Zabaneh</t>
+          <t>Jamalzadeh</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -4009,12 +4017,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Aria</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Fernandes</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -4027,15 +4035,19 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Maggie</t>
+          <t>ali</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Chiu</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
+          <t>karimi</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>alikarimi1313@hotmail.com</t>
+        </is>
+      </c>
       <c r="D183" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4045,15 +4057,19 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Nirmaljeet</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Singh</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr"/>
+          <t>Ritcey</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>sueritcey@gmail.com</t>
+        </is>
+      </c>
       <c r="D184" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4063,19 +4079,15 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Brian J</t>
+          <t>Zaina</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Quinlan</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>brianquinlan@sympatico.ca</t>
-        </is>
-      </c>
+          <t>Zabaneh</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4085,12 +4097,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>diana</t>
+          <t>Aria</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Dodd</t>
+          <t>Fernandes</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4103,12 +4115,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Maggie</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Chiu</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -4121,12 +4133,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Emmanuel</t>
+          <t>Nirmaljeet</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4139,15 +4151,19 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Ashley</t>
+          <t>Brian J</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Huang</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr"/>
+          <t>Quinlan</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>brianquinlan@sympatico.ca</t>
+        </is>
+      </c>
       <c r="D189" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4157,12 +4173,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Jasmine</t>
+          <t>diana</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Xiao</t>
+          <t>Dodd</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -4175,7 +4191,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Bruce</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4193,12 +4209,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>STEVEN</t>
+          <t>Emmanuel</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -4211,12 +4227,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>Ashley</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Yang</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -4229,12 +4245,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Janina</t>
+          <t>Jasmine</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>KLOPSCH</t>
+          <t>Xiao</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -4247,19 +4263,15 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Bruce</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Easey</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>jenroberts6@gmail.com</t>
-        </is>
-      </c>
+          <t>Wong</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4269,12 +4281,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>STEVEN</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4287,12 +4299,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Hendrik</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>VanderMeulen</t>
+          <t>Yang</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -4305,12 +4317,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Justus</t>
+          <t>Janina</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>KLOPSCH</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -4323,15 +4335,19 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr"/>
+          <t>Easey</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>jenroberts6@gmail.com</t>
+        </is>
+      </c>
       <c r="D199" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4341,12 +4357,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Esther</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -4359,12 +4375,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Tammie</t>
+          <t>Hendrik</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Fong</t>
+          <t>VanderMeulen</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -4377,12 +4393,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Justus</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Yin</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -4395,12 +4411,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Bennett</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -4413,12 +4429,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Esther</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Macdonald</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -4431,12 +4447,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Suhanee</t>
+          <t>Tammie</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Sood</t>
+          <t>Fong</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -4449,12 +4465,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Mylo</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Yin</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -4467,19 +4483,15 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Couse</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>jcouse@segalgcse.com</t>
-        </is>
-      </c>
+          <t>Bennett</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4489,12 +4501,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Josiah</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Macdonald</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -4507,12 +4519,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Suhanee</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Aceto</t>
+          <t>Sood</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -4525,7 +4537,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Brad</t>
+          <t>Mylo</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4543,15 +4555,19 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Cotton</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr"/>
+          <t>Couse</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>jcouse@segalgcse.com</t>
+        </is>
+      </c>
       <c r="D211" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4561,12 +4577,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Vic</t>
+          <t>Josiah</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Suan</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -4579,19 +4595,15 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Cummings</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>mwcummings@hotmail.ca</t>
-        </is>
-      </c>
+          <t>Aceto</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4601,12 +4613,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Hua</t>
+          <t>Brad</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Shi</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -4619,12 +4631,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Gila</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Kohen Rydlewicz</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -4637,12 +4649,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Vic</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Aceto</t>
+          <t>Suan</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -4655,15 +4667,19 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Care</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Dodd</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr"/>
+          <t>Cummings</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>mwcummings@hotmail.ca</t>
+        </is>
+      </c>
       <c r="D217" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4673,12 +4689,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Godfrey</t>
+          <t>Hua</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Yeung</t>
+          <t>Shi</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -4691,19 +4707,15 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>claudine</t>
+          <t>Gila</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Lukawesky</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>davidclaudie@sympatico.ca</t>
-        </is>
-      </c>
+          <t>Kohen Rydlewicz</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4713,12 +4725,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Suan</t>
+          <t>Aceto</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -4731,12 +4743,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Care</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Dodd</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -4749,12 +4761,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Kieran</t>
+          <t>Godfrey</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Lai</t>
+          <t>Yeung</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -4767,17 +4779,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Hafsa</t>
+          <t>claudine</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Esmail</t>
+          <t>Lukawesky</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>admin@powerofwordsacademy.ca</t>
+          <t>davidclaudie@sympatico.ca</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -4789,12 +4801,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Darryl</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Fortes</t>
+          <t>Suan</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -4807,12 +4819,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Henrietta</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Tsui</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -4825,12 +4837,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Kieran</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Simunovic</t>
+          <t>Lai</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -4843,15 +4855,19 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Cole</t>
+          <t>Hafsa</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Billinkoff</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr"/>
+          <t>Esmail</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>admin@powerofwordsacademy.ca</t>
+        </is>
+      </c>
       <c r="D227" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4861,12 +4877,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Bobby</t>
+          <t>Darryl</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Cancelli</t>
+          <t>Fortes</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -4879,12 +4895,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Jake</t>
+          <t>Henrietta</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Billinkoff</t>
+          <t>Tsui</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -4897,12 +4913,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Jennie</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Mohabir</t>
+          <t>Simunovic</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -4915,12 +4931,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Rachelle</t>
+          <t>Cole</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Billinkoff</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -4933,12 +4949,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Bobby</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Girard</t>
+          <t>Cancelli</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -4951,19 +4967,15 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Jake</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Natan</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>lior797@gmail.com</t>
-        </is>
-      </c>
+          <t>Billinkoff</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -4973,12 +4985,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Kathleen</t>
+          <t>Jennie</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Nadon</t>
+          <t>Mohabir</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -4991,12 +5003,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Rachelle</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Nadon</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -5009,12 +5021,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Teos</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Vaccaro</t>
+          <t>Girard</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -5027,15 +5039,19 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Jackie</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Chan</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr"/>
+          <t>Natan</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>lior797@gmail.com</t>
+        </is>
+      </c>
       <c r="D237" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5045,12 +5061,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Jisoo</t>
+          <t>Kathleen</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Maynard</t>
+          <t>Nadon</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -5063,19 +5079,15 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Kwong</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>331.kwong@gmail.com</t>
-        </is>
-      </c>
+          <t>Nadon</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5085,12 +5097,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Teos</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Karam</t>
+          <t>Vaccaro</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -5103,12 +5115,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Jackie</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Almaria</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -5121,12 +5133,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Sisily</t>
+          <t>Jisoo</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Solis</t>
+          <t>Maynard</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -5139,15 +5151,19 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Lilybeth</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Solis</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr"/>
+          <t>Kwong</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>331.kwong@gmail.com</t>
+        </is>
+      </c>
       <c r="D243" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5157,12 +5173,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Teos</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Vaccaro</t>
+          <t>Karam</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -5175,12 +5191,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Ksenia</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Vaccaro</t>
+          <t>Almaria</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -5193,12 +5209,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Sisily</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Nicholl</t>
+          <t>Solis</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -5211,12 +5227,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Lilybeth</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Nicholl</t>
+          <t>Solis</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -5229,12 +5245,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Teos</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Tay</t>
+          <t>Vaccaro</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -5247,12 +5263,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Asllan</t>
+          <t>Ksenia</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Vaccaro</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -5265,12 +5281,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Giselle</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Del Rosario</t>
+          <t>Nicholl</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -5283,12 +5299,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Jenkins</t>
+          <t>Nicholl</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -5301,12 +5317,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Chin</t>
+          <t>Tay</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -5319,12 +5335,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Asllan</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Cheung</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -5337,12 +5353,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Kiara</t>
+          <t>Giselle</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Bici</t>
+          <t>Del Rosario</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -5355,12 +5371,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Jin</t>
+          <t>Jenkins</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -5373,12 +5389,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Vicky</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Su</t>
+          <t>Chin</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -5391,12 +5407,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Pileggi</t>
+          <t>Cheung</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -5409,12 +5425,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Fiona</t>
+          <t>Kiara</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Bici</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -5427,12 +5443,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Brittany</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Horan</t>
+          <t>Jin</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -5445,12 +5461,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Vicky</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Folletet</t>
+          <t>Su</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -5463,12 +5479,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Ruchira</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Kulkarni</t>
+          <t>Pileggi</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -5481,12 +5497,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Annie</t>
+          <t>Fiona</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Tran</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -5499,12 +5515,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Lilian</t>
+          <t>Brittany</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Jiang</t>
+          <t>Horan</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -5517,12 +5533,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Folletet</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -5535,12 +5551,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Pamela</t>
+          <t>Ruchira</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Ip</t>
+          <t>Kulkarni</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -5553,19 +5569,15 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Annie</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>samherson@hotmail.com</t>
-        </is>
-      </c>
+          <t>Tran</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5575,12 +5587,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Dana</t>
+          <t>Lilian</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>Jiang</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -5593,19 +5605,15 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Reah Angelee</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Saldivar</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>reahangeleesldvr@yahoo.com</t>
-        </is>
-      </c>
+          <t>Lam</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5615,12 +5623,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Pamela</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Kitt</t>
+          <t>Ip</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -5633,17 +5641,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Andy</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>andydnguyen92@gmail.com</t>
+          <t>samherson@hotmail.com</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -5655,12 +5663,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Mack</t>
+          <t>Dana</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Lapointe</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -5673,19 +5681,15 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Jay</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Latiff</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>jaythefungi@proton.me</t>
-        </is>
-      </c>
+          <t>Kitt</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5695,15 +5699,19 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Lin</t>
+          <t>Andy</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Lu</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr"/>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>andydnguyen92@gmail.com</t>
+        </is>
+      </c>
       <c r="D273" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5713,12 +5721,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Mikhael</t>
+          <t>Mack</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>Lapointe</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -5731,15 +5739,19 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Anh</t>
+          <t>Jinze</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr"/>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>jinze.0804@gmail.com</t>
+        </is>
+      </c>
       <c r="D275" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5749,15 +5761,19 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Jay</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Cheung</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr"/>
+          <t>Latiff</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>jaythefungi@proton.me</t>
+        </is>
+      </c>
       <c r="D276" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5767,19 +5783,15 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Liza</t>
+          <t>Lin</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Benkovitch</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>liza@d8teclub.com</t>
-        </is>
-      </c>
+          <t>Lu</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5789,12 +5801,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Patricio</t>
+          <t>Mikhael</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Dávalos ucha</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -5807,19 +5819,15 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>christopher</t>
+          <t>Anh</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Go Bio</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>pilyo311@gmail.com</t>
-        </is>
-      </c>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5829,19 +5837,15 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Kristy</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>kristysuen23@gmail.com</t>
-        </is>
-      </c>
+          <t>Cheung</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5851,17 +5855,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Liza</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Rodrigues</t>
+          <t>Benkovitch</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>nrodrigues@cihi.ca</t>
+          <t>liza@d8teclub.com</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -5873,12 +5877,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Duy</t>
+          <t>Patricio</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Ho</t>
+          <t>Dávalos ucha</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -5891,15 +5895,19 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Nasim</t>
+          <t>Claudia</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Hashemi</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr"/>
+          <t>Diverio De Faria</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>claudiadiverio@gmail.com</t>
+        </is>
+      </c>
       <c r="D283" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5909,17 +5917,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>christopher</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Cui</t>
+          <t>Go Bio</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>everydayisgreat777@gmail.com</t>
+          <t>pilyo311@gmail.com</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -5931,15 +5939,19 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Ashley</t>
+          <t>Kristy</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Vu</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr"/>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>kristysuen23@gmail.com</t>
+        </is>
+      </c>
       <c r="D285" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5949,15 +5961,19 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Dong</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr"/>
+          <t>Rodrigues</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>nrodrigues@cihi.ca</t>
+        </is>
+      </c>
       <c r="D286" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -5967,12 +5983,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Daisy</t>
+          <t>Duy</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Xu</t>
+          <t>Ho</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -5985,12 +6001,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Nasim</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Kat</t>
+          <t>Hashemi</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -6003,17 +6019,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Bhamra</t>
+          <t>Cui</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>simranb1395@gmail.com</t>
+          <t>everydayisgreat777@gmail.com</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -6025,15 +6041,19 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Shikha</t>
+          <t>Yulin</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Kothari</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr"/>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>yulin1chen@gmail.com</t>
+        </is>
+      </c>
       <c r="D290" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6043,19 +6063,15 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Prags</t>
+          <t>Ashley</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Manickam</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>pragcan96@gmail.com</t>
-        </is>
-      </c>
+          <t>Vu</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6065,17 +6081,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Kate</t>
+          <t>Akanksha</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Kom</t>
+          <t>Dutta</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>katekim@live.com</t>
+          <t>akanksha.dutta@yahoo.co.in</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -6087,12 +6103,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Timosa</t>
+          <t>Dong</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
@@ -6105,12 +6121,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Daisy</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Davis</t>
+          <t>Xu</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -6123,12 +6139,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Hsieh</t>
+          <t>Kat</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -6141,17 +6157,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Ko</t>
+          <t>Bhamra</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>rebecca.ko@jig.to</t>
+          <t>simranb1395@gmail.com</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -6163,19 +6179,15 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Urvashi</t>
+          <t>Shikha</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Chauhan</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>urvashi.chauhan@clearscore.com</t>
-        </is>
-      </c>
+          <t>Kothari</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6185,15 +6197,19 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Bryan</t>
+          <t>Prags</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Nguyen</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr"/>
+          <t>Manickam</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>pragcan96@gmail.com</t>
+        </is>
+      </c>
       <c r="D298" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6203,17 +6219,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Chi</t>
+          <t>Kate</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Quach</t>
+          <t>Kom</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>mesamune@hotmail.com</t>
+          <t>katekim@live.com</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -6225,12 +6241,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Del rosario</t>
+          <t>Timosa</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
@@ -6243,19 +6259,15 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Sumati</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Singh</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>sumati.singh@outlook.com</t>
-        </is>
-      </c>
+          <t>Davis</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6265,12 +6277,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Cooney</t>
+          <t>Hsieh</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
@@ -6283,15 +6295,19 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Galina</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Lad</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr"/>
+          <t>Torres</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>julia.torres@live.ca</t>
+        </is>
+      </c>
       <c r="D303" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6301,15 +6317,19 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Liam</t>
+          <t>Rebecca</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Cooney</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr"/>
+          <t>Ko</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>rebecca.ko@jig.to</t>
+        </is>
+      </c>
       <c r="D304" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6319,15 +6339,19 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Sahar</t>
+          <t>Urvashi</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr"/>
+          <t>Chauhan</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>urvashi.chauhan@clearscore.com</t>
+        </is>
+      </c>
       <c r="D305" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6337,15 +6361,19 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Arav</t>
+          <t>Irene</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr"/>
+          <t>Cabading</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>irene10tm@gmail.com</t>
+        </is>
+      </c>
       <c r="D306" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6355,12 +6383,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Salama</t>
+          <t>Bryan</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Karim</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -6373,15 +6401,19 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Jake Denver</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Williams</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr"/>
+          <t>Enriquez</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>jake.business1017@outlook.com</t>
+        </is>
+      </c>
       <c r="D308" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6391,15 +6423,19 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Bryan</t>
+          <t>Chi</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Nguyen</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr"/>
+          <t>Quach</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>mesamune@hotmail.com</t>
+        </is>
+      </c>
       <c r="D309" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6409,12 +6445,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Nix</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Cochangco</t>
+          <t>Del rosario</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
@@ -6427,17 +6463,17 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Sumati</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Yang</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>sharon.ca@hotmail.com</t>
+          <t>sumati.singh@outlook.com</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -6449,15 +6485,19 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Lukas</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Szczurowski</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr"/>
+          <t>Jeon</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>wjsaughks100@gmail.com</t>
+        </is>
+      </c>
       <c r="D312" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6467,12 +6507,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Malks</t>
+          <t>Cooney</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -6485,12 +6525,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Miles</t>
+          <t>Galina</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Malks</t>
+          <t>Lad</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
@@ -6503,12 +6543,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Kaitlyn</t>
+          <t>Liam</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Cooney</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -6521,12 +6561,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Sahar</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -6539,19 +6579,15 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Carly</t>
+          <t>Arav</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Handler</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>handlerc97@gmail.com</t>
-        </is>
-      </c>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6561,19 +6597,15 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Vinay</t>
+          <t>Salama</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Amarnani</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>vinay.amarnani1@gmail.com</t>
-        </is>
-      </c>
+          <t>Karim</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6583,19 +6615,15 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>alan</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>tsang</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>altsanghk@hotmail.com</t>
-        </is>
-      </c>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6605,19 +6633,15 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>Bryan</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>untitled.tif@gmail.com</t>
-        </is>
-      </c>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6627,12 +6651,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Ingrid</t>
+          <t>Nix</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Suhardja</t>
+          <t>Cochangco</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -6645,17 +6669,17 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Shivangi</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Garg</t>
+          <t>Yang</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>canada.sgarg@gmail.com</t>
+          <t>sharon.ca@hotmail.com</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -6667,19 +6691,15 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Poling</t>
+          <t>Lukas</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Pan</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>poling.pan0319@gmail.com</t>
-        </is>
-      </c>
+          <t>Szczurowski</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6689,19 +6709,15 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Siya</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Garg</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>siyagarg.canada@gmail.com</t>
-        </is>
-      </c>
+          <t>Malks</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6711,19 +6727,15 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Mahir</t>
+          <t>Miles</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Shaikh</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>mahirthebest95@gmail.com</t>
-        </is>
-      </c>
+          <t>Malks</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6733,19 +6745,15 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Shayan</t>
+          <t>Kaitlyn</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Abbasi</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>abbasi.shayan1995@gmail.com</t>
-        </is>
-      </c>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6755,12 +6763,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>kHUSHAAN</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Garg</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
@@ -6773,17 +6781,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Elliot</t>
+          <t>Carly</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Bhamani</t>
+          <t>Handler</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>elliot.bhamani@gmail.com</t>
+          <t>handlerc97@gmail.com</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -6795,17 +6803,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Danielle</t>
+          <t>Vinay</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Amarnani</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>catania.danielle@gmail.com</t>
+          <t>vinay.amarnani1@gmail.com</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -6817,17 +6825,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Amir</t>
+          <t>alan</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Nouraein</t>
+          <t>tsang</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>parhamnuri@gmail.com</t>
+          <t>altsanghk@hotmail.com</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -6839,15 +6847,19 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Vania</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Garg</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr"/>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>untitled.tif@gmail.com</t>
+        </is>
+      </c>
       <c r="D331" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6857,19 +6869,15 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Kit</t>
+          <t>Ingrid</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Yiu</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>hungkityiu@gmail.com</t>
-        </is>
-      </c>
+          <t>Suhardja</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6879,15 +6887,19 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Simom</t>
+          <t>Shivangi</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Yim</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr"/>
+          <t>Garg</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>canada.sgarg@gmail.com</t>
+        </is>
+      </c>
       <c r="D333" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6897,17 +6909,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Emmy</t>
+          <t>Poling</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Cao</t>
+          <t>Pan</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>emmy.cao@zoocasa.com</t>
+          <t>poling.pan0319@gmail.com</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -6919,17 +6931,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Hanny</t>
+          <t>Siya</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Chau</t>
+          <t>Garg</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>hanny.chau@outlook.com</t>
+          <t>siyagarg.canada@gmail.com</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -6941,17 +6953,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Mahir</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Nestico</t>
+          <t>Shaikh</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>thomasjamesnestico@gmail.com</t>
+          <t>mahirthebest95@gmail.com</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -6963,15 +6975,19 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Shayan</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Chau</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr"/>
+          <t>Abbasi</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>abbasi.shayan1995@gmail.com</t>
+        </is>
+      </c>
       <c r="D337" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -6981,12 +6997,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>kHUSHAAN</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Chau</t>
+          <t>Garg</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
@@ -6999,17 +7015,17 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Ishaan</t>
+          <t>Elliot</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Mehta</t>
+          <t>Bhamani</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>mehtaishaan4@gmail.com</t>
+          <t>elliot.bhamani@gmail.com</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -7021,15 +7037,19 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Zimo</t>
+          <t>Danielle</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Chen</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr"/>
+          <t>Catania</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>catania.danielle@gmail.com</t>
+        </is>
+      </c>
       <c r="D340" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7039,17 +7059,17 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Amir</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>Nouraein</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>utgw01@gmail.com</t>
+          <t>parhamnuri@gmail.com</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -7061,19 +7081,15 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Terry</t>
+          <t>Vania</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Wang</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>jiaxiangw0@gmail.com</t>
-        </is>
-      </c>
+          <t>Garg</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7083,17 +7099,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>arjun</t>
+          <t>Kit</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>kapur</t>
+          <t>Yiu</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>arjun.ak67@gmail.com</t>
+          <t>hungkityiu@gmail.com</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -7105,19 +7121,15 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Simom</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Chen</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>heinhtet1995@gmail.com</t>
-        </is>
-      </c>
+          <t>Yim</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7127,17 +7139,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Bonnie</t>
+          <t>Emmy</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Cao</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>blam@cihi.ca</t>
+          <t>emmy.cao@zoocasa.com</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -7149,17 +7161,17 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Hanny</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Chau</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>linda33440@gmail.com</t>
+          <t>hanny.chau@outlook.com</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -7171,17 +7183,17 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Yang</t>
+          <t>Nestico</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>michael_yang@live.com</t>
+          <t>thomasjamesnestico@gmail.com</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -7193,19 +7205,15 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Jasmine</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Huang</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>qiuminhuang@gmail.com</t>
-        </is>
-      </c>
+          <t>Chau</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7215,19 +7223,15 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Zhenzhen</t>
+          <t>Tyler</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Wang</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>wzzheloise@gmail.com</t>
-        </is>
-      </c>
+          <t>Chau</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7237,17 +7241,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Wesley</t>
+          <t>Ishaan</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Lin</t>
+          <t>Mehta</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>wesley.linvan@gmail.com</t>
+          <t>mehtaishaan4@gmail.com</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -7259,19 +7263,15 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Nischaye</t>
+          <t>Zimo</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Ramparsad</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>nischaye05@gmail.com</t>
-        </is>
-      </c>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7281,17 +7281,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Yiu</t>
+          <t>King</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>tiff.y7281@gmail.com</t>
+          <t>utgw01@gmail.com</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -7303,17 +7303,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Shuqin</t>
+          <t>Terry</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Xia</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>525160331@qq.com</t>
+          <t>jiaxiangw0@gmail.com</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -7325,17 +7325,17 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>jun</t>
+          <t>arjun</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>ji</t>
+          <t>kapur</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>wilson277@live.com</t>
+          <t>arjun.ak67@gmail.com</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -7347,17 +7347,17 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Mehar</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Nakai</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>meharnakai@gmail.com</t>
+          <t>heinhtet1995@gmail.com</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -7369,15 +7369,19 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Bonnie</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr"/>
+          <t>Lam</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>blam@cihi.ca</t>
+        </is>
+      </c>
       <c r="D356" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7387,17 +7391,17 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>McKee</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>robertmckee286@gmail.com</t>
+          <t>linda33440@gmail.com</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -7409,17 +7413,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Xianming</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Zhu</t>
+          <t>Yang</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>xianmingzhu@gmail.com</t>
+          <t>michael_yang@live.com</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -7439,7 +7443,11 @@
           <t>Huang</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr"/>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>qiuminhuang@gmail.com</t>
+        </is>
+      </c>
       <c r="D359" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7449,17 +7457,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Wei</t>
+          <t>Zhenzhen</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Hou</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>weihou99@yahoo.com</t>
+          <t>wzzheloise@gmail.com</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -7471,17 +7479,17 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Wesley</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Andrews</t>
+          <t>Lin</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>ewandrews@bell.net</t>
+          <t>wesley.linvan@gmail.com</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -7493,17 +7501,17 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Claire</t>
+          <t>Nischaye</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Gregorio</t>
+          <t>Ramparsad</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>claire.gregorio512@gmail.com</t>
+          <t>nischaye05@gmail.com</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -7515,17 +7523,17 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Joeeph</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Atkinson-Orlando</t>
+          <t>Yiu</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>josephao@rogers.com</t>
+          <t>tiff.y7281@gmail.com</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -7537,17 +7545,17 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Debahuti</t>
+          <t>Shuqin</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Basu</t>
+          <t>Xia</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>debahuti@gmail.com</t>
+          <t>525160331@qq.com</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -7559,17 +7567,17 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Bryan</t>
+          <t>jun</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>ji</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>bryanchen2013@gmail.com</t>
+          <t>wilson277@live.com</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -7581,17 +7589,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Mehar</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Nakai</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>johnt.xaos@gmail.com</t>
+          <t>meharnakai@gmail.com</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -7603,19 +7611,15 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>BIN</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>WANG</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>binwcs@gmail.com</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7625,17 +7629,17 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Shirley</t>
+          <t>Rob</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>McKee</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>shirleyc2020.2020@gmail.com</t>
+          <t>robertmckee286@gmail.com</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -7647,17 +7651,17 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Varun</t>
+          <t>Xianming</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Sondhi</t>
+          <t>Zhu</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>sondhi.varun@gmail.com</t>
+          <t>xianmingzhu@gmail.com</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -7669,19 +7673,15 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Jasmine</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Rose</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>markdavidrose0@gmail.com</t>
-        </is>
-      </c>
+          <t>Huang</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
@@ -7691,17 +7691,17 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Dina</t>
+          <t>Wei</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Pantaleon</t>
+          <t>Hou</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>gotsoul27@gmail.com</t>
+          <t>weihou99@yahoo.com</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -7713,17 +7713,17 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Hugo</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Tran</t>
+          <t>Andrews</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>nismoboy1992@gmail.com</t>
+          <t>ewandrews@bell.net</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -7735,17 +7735,17 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Claire</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Williamson</t>
+          <t>Gregorio</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>michaelrwilliamson2@gmail.com</t>
+          <t>claire.gregorio512@gmail.com</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -7757,17 +7757,17 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Mayuresh</t>
+          <t>Joeeph</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Sawant</t>
+          <t>Atkinson-Orlando</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>mayuresh.sawant@live.in</t>
+          <t>josephao@rogers.com</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -7779,17 +7779,17 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Helen</t>
+          <t>Debahuti</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Im</t>
+          <t>Basu</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>helenim3@gmail.com</t>
+          <t>debahuti@gmail.com</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -7801,17 +7801,17 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Nicole</t>
+          <t>Bryan</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Maroon</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>nicolemaroon@gmail.com</t>
+          <t>bryanchen2013@gmail.com</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -7823,20 +7823,740 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Turner</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>johnt.xaos@gmail.com</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>BIN</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>WANG</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>binwcs@gmail.com</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Shirley</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>shirleyc2020.2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Varun</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Sondhi</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>sondhi.varun@gmail.com</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>markdavidrose0@gmail.com</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Dina</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Pantaleon</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>gotsoul27@gmail.com</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Williamson</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>michaelrwilliamson2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Mayuresh</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Sawant</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>mayuresh.sawant@live.in</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Helen</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Im</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>helenim3@gmail.com</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Maroon</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>nicolemaroon@gmail.com</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
           <t>Viada Marie</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr">
+      <c r="B387" t="inlineStr">
         <is>
           <t>Cauyao</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr">
+      <c r="C387" t="inlineStr">
         <is>
           <t>viadamariecauyao2442@gmail.com</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr">
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Deng</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>ryanyld.9013@gmail.com</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Torres</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Chloe</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Torres-Parent</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Cyle</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Amigleo</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Jezrell</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Torres</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Tyson</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Rakesh</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Alluri</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>rakeshbuy@gmail.com</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Suzuki</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Sayako</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>suzuki.sayako@fourseasons.com</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Therese</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Henriksson</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>athereseh92@gmail.com</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Brittany</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Stenekes</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>britt.stenekes@gmail.com</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Christina</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Chung</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>christinachung09@gmail.com</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>NATALIE</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>THOMPSON</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>natthompson2015@gmail.com</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Jess</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Cheng</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>jess.yk.cheng@gmail.com</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Sangmin</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Park</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>atkdalsa@gmail.com</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>AnnAua Shahahanna</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Bendijo</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Ankur</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Toye</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>ankurtoye@gmail.com</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Joo</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>songjoo29@gmail.com</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Winnie</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Siao</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>winniesiao@gmail.com</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Grant Robert</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Labastida</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Edwin</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Chung</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>edwinchung.tds@gmail.com</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Arsam</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Asaf</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>arsam.asaf@gmail.com</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Sax</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>david@saxmail.ca</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Daphne</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Jara-Charbonneau</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>dj.charbonneau18@gmail.com</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>yorkmills@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Tala</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Abdelmaguud</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>tala.abdelmaguid@gmail.com</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
         <is>
           <t>yorkmills@pickleplex.ca</t>
         </is>
